--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,16 +77,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -454,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -612,7 +617,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미 실적시즌 메가캡 테크·헬스케어 서프라이즈로 3대지수 동반 강세, 반면 중화권은 광모듈·반도체 급락 vs 은행 고배당 순환매로 양극화 국면.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美: 나스닥 +2.78%·S&amp;P +1.66%·다우 +1.19%. 강세는 금융(순강도+10)·헬스(+6, CORT +27%·REGN·ILMN 실적호조), XLK 테크ETF +5.5%로 메가캡 주도. 약세는 Producer Manufacturing(순강도-7)·담배 알트리아 -9%·방산 L3해리스 -8.6%·물류 CH로빈슨 -15% 실적 실망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日: 은행ETF -3.4%·자동차 -2.2% 약세 우위, 전기정밀 +2.5%(NEC 1분기 순익 2.6배로 +8%). 마키타 관세환급 일회성에 -10%, 주부전력 적자전환·키오시아 메모리 우려로 신저가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 中·홍콩: 상해 -0.62%·CSI300 -1.10%·항셍테크 -1.25%. 공통 축은 은행(순강도 中+9/홍+7) 고배당 순환매로 신고가 vs AI 하드웨어 급락(中 전자기술 순강도 -16). 中지쉬촹 홍콩 IPO 첫날 붕괴에 광모듈(신이성·톈푸퉁신 등) 동반 급락, 홍콩 중신궈지 -7.7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①남은 미 메가캡 실적·AI capex 코멘트 ②중화권 광모듈·반도체 조정 지속 여부 ③은행 방어 순환매 지속성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -710,19 +750,19 @@
       <c r="C2" t="n">
         <v>7437.63</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>-0.82</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>4.23</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>8.65</v>
       </c>
       <c r="I2" t="n">
@@ -748,19 +788,19 @@
       <c r="C3" t="n">
         <v>25122.18</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>2.78</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>-4.16</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>8.09</v>
       </c>
       <c r="I3" t="n">
@@ -786,19 +826,19 @@
       <c r="C4" t="n">
         <v>5663.24</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-5.98</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-16.69</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-32.54</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-12.55</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>34.39</v>
       </c>
       <c r="I4" t="n">
@@ -824,19 +864,19 @@
       <c r="C5" t="n">
         <v>61434.19</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-1.49</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-7.08</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-11.56</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>2.88</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>22.04</v>
       </c>
       <c r="I5" t="n">
@@ -860,11 +900,11 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -880,11 +920,11 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
@@ -900,11 +940,11 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
@@ -920,11 +960,11 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
     </row>
@@ -1023,7 +1063,7 @@
       <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1058,7 +1098,7 @@
       <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1093,7 +1133,7 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1128,7 +1168,7 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1163,7 +1203,7 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1198,7 +1238,7 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1233,7 +1273,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1268,7 +1308,7 @@
       <c r="F9" t="n">
         <v>-1</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1303,7 +1343,7 @@
       <c r="F10" t="n">
         <v>-2</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1338,7 +1378,7 @@
       <c r="F11" t="n">
         <v>-2</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1373,7 +1413,7 @@
       <c r="F12" t="n">
         <v>-2</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1408,7 +1448,7 @@
       <c r="F13" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1443,7 +1483,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1478,7 +1518,7 @@
       <c r="F15" t="n">
         <v>-7</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1723,7 +1763,7 @@
       <c r="F22" t="n">
         <v>6</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1758,7 +1798,7 @@
       <c r="F23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1793,7 +1833,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1828,7 +1868,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1863,7 +1903,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1898,7 +1938,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1933,7 +1973,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1968,7 +2008,7 @@
       <c r="F29" t="n">
         <v>-1</v>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2003,7 +2043,7 @@
       <c r="F30" t="n">
         <v>-1</v>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2038,7 +2078,7 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2073,7 +2113,7 @@
       <c r="F32" t="n">
         <v>-1</v>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2353,7 +2393,7 @@
       <c r="F40" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2388,7 +2428,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2423,7 +2463,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2458,7 +2498,7 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2493,7 +2533,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2528,7 +2568,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2563,7 +2603,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2598,7 +2638,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2633,7 +2673,7 @@
       <c r="F48" t="n">
         <v>-3</v>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2668,7 +2708,7 @@
       <c r="F49" t="n">
         <v>-6</v>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2983,7 +3023,7 @@
       <c r="F58" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3018,7 +3058,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3053,7 +3093,7 @@
       <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3088,7 +3128,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3123,7 +3163,7 @@
       <c r="F62" t="n">
         <v>-1</v>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3156,7 +3196,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3191,7 +3231,7 @@
       <c r="F64" t="n">
         <v>-2</v>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3226,7 +3266,7 @@
       <c r="F65" t="n">
         <v>-2</v>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3261,7 +3301,7 @@
       <c r="F66" t="n">
         <v>-7</v>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3296,7 +3336,7 @@
       <c r="F67" t="n">
         <v>-16</v>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3605,30 +3645,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3649,90 +3690,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -3754,58 +3800,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>메가캡 테크 실적 서프라이즈로 당일 +5.5% 급등, 다만 전자기술 순강도 -2로 breadth는 대형주 편중</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="F2" s="10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="10" t="n">
         <v>-7.8</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="10" t="n">
         <v>10.6</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="I2" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="K2" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="M2" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="O2" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="Q2" s="10" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="7" t="n">
+      <c r="S2" s="10" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="7" t="n">
+      <c r="U2" s="10" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3825,58 +3876,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>CORT +27%·REGN·ILMN 개별 실적주 강세, 다만 ALNY -28% 미스 혼재로 ETF -1.6%</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="10" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="Q3" s="10" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="7" t="n">
+      <c r="S3" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="7" t="n">
+      <c r="U3" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3896,58 +3952,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>신고-신저 순강도 +10 전 섹터 최강, 은행·보험 신고가 다수로 가치·방어 선호(+0.6%)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="F4" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="10" t="n">
         <v>6.3</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="I4" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="K4" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="M4" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="O4" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="Q4" s="10" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="S4" s="10" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="U4" s="10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3967,58 +4028,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>치폴레 +12.5% 등 외식·서비스 실적 개선에 당일 +0.7%</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="G5" s="10" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="10" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="I5" s="10" t="n">
         <v>-5.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="K5" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="O5" s="10" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="Q5" s="10" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="S5" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="U5" s="10" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4038,58 +4104,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>당일 -2.7%로 전 섹터 최약, 광고·미디어 대형주 실적 경계</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="10" t="n">
         <v>-7.3</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="10" t="n">
         <v>-8.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="10" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="O6" s="10" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="Q6" s="10" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="S6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="U6" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4109,58 +4180,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>ETF +1.0%에도 Producer Manufacturing 순강도 -7로 breadth 약세, 방산 L3해리스 -8.6% 신저가</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F7" s="10" t="n">
         <v>-2</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="10" t="n">
         <v>-3.7</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="10" t="n">
         <v>15.6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="K7" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="10" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="O7" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="Q7" s="10" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="S7" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="U7" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4180,58 +4256,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>담배 알트리아 -9.3% 실적 실망 등으로 당일 -2.2% 약세</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="10" t="n">
         <v>3.8</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I8" s="10" t="n">
         <v>11.4</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="K8" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="O8" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="Q8" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="S8" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="U8" s="10" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4251,58 +4332,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>1개월 +11%로 상대강세 지속, 당일 +0.5%</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="F9" s="10" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="H9" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="I9" s="10" t="n">
         <v>33.7</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="K9" s="10" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="M9" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="O9" s="10" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="Q9" s="10" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="7" t="n">
+      <c r="S9" s="10" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="7" t="n">
+      <c r="U9" s="10" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4322,58 +4408,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>당일 -0.6% 소폭 약세, 뚜렷한 촉매 없음</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="F10" s="10" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="10" t="n">
         <v>-1.6</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="I10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="O10" s="10" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4393,58 +4484,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>당일 -0.2% 보합권, 방향성 부재</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="F11" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="H11" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="I11" s="10" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="K11" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="M11" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="O11" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="Q11" s="10" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="S11" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="U11" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4464,58 +4560,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ETF -1.4% 약세이나 JLL +6.4% 실적 서프라이즈로 52주 신고가 개별 차별화</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="F12" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="G12" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="H12" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="I12" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="K12" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="M12" s="10" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="O12" s="10" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="Q12" s="10" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="S12" s="10" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="U12" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4535,58 +4636,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="10" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="F13" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="G13" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="H13" s="10" t="n">
         <v>12.1</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="I13" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="K13" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="M13" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="O13" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="Q13" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="S13" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="U13" s="10" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4606,58 +4708,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="F14" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="H14" s="10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="I14" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="K14" s="10" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="M14" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="O14" s="10" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="Q14" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="S14" s="10" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="U14" s="10" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4677,58 +4780,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="F15" s="10" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="10" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="I15" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="K15" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="O15" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="Q15" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="S15" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="U15" s="10" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4748,58 +4852,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="F16" s="10" t="n">
         <v>-5.9</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="G16" s="10" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="H16" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="I16" s="10" t="n">
         <v>17.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="K16" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="M16" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="O16" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="Q16" s="10" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="S16" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="U16" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4819,58 +4924,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="F17" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="10" t="n">
         <v>5.4</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="H17" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="I17" s="10" t="n">
         <v>5.1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="K17" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="M17" s="10" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="O17" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="Q17" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="S17" s="10" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="U17" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4890,58 +4996,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="F18" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="G18" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="H18" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="I18" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="K18" s="10" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="M18" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="O18" s="10" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="Q18" s="10" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="S18" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="U18" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4961,58 +5068,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="F19" s="10" t="n">
         <v>-11.8</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="G19" s="10" t="n">
         <v>-22.3</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="H19" s="10" t="n">
         <v>-21.8</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="I19" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="K19" s="10" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="M19" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="O19" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="Q19" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="S19" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="U19" s="10" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5032,58 +5140,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="F20" s="10" t="n">
         <v>-5.7</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="G20" s="10" t="n">
         <v>-6.3</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="H20" s="10" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="I20" s="10" t="n">
         <v>14.5</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="K20" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="M20" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="O20" s="10" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="Q20" s="10" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="S20" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="U20" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5103,58 +5212,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="F21" s="10" t="n">
         <v>-6.7</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="G21" s="10" t="n">
         <v>-14.3</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="H21" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="I21" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="K21" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="M21" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="O21" s="10" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="Q21" s="10" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="S21" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="U21" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5174,58 +5284,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="10" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="F22" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="G22" s="10" t="n">
         <v>5.7</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="H22" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="I22" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>12</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="K22" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="O22" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="Q22" s="10" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="S22" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="U22" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5245,58 +5356,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="F23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="H23" s="10" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="I23" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="K23" s="10" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="M23" s="10" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="O23" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="Q23" s="10" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="S23" s="10" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="U23" s="10" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5316,58 +5428,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="10" t="n">
         <v>-2</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="F24" s="10" t="n">
         <v>4.2</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="G24" s="10" t="n">
         <v>10.6</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="H24" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="I24" s="10" t="n">
         <v>7.2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>11</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="K24" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="M24" s="10" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="O24" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="Q24" s="10" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="S24" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="U24" s="10" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5387,58 +5500,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="F25" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="G25" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="H25" s="10" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="I25" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="K25" s="10" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="M25" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="O25" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="Q25" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="7" t="n">
+      <c r="S25" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="7" t="n">
+      <c r="U25" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5458,58 +5572,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="10" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="F26" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="G26" s="10" t="n">
         <v>5.4</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="H26" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="I26" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="K26" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="M26" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="O26" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="Q26" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="S26" s="10" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="U26" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5529,58 +5644,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="10" t="n">
         <v>-3.4</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="F27" s="10" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="G27" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="H27" s="10" t="n">
         <v>22.9</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="I27" s="10" t="n">
         <v>40.7</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="K27" s="10" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="M27" s="10" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="O27" s="10" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="Q27" s="10" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="7" t="n">
+      <c r="S27" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="7" t="n">
+      <c r="U27" s="10" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5600,58 +5716,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="F28" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="G28" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="H28" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="I28" s="10" t="n">
         <v>31.6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="K28" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="M28" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="O28" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="Q28" s="10" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="S28" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="7" t="n">
+      <c r="U28" s="10" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5671,58 +5788,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="10" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="F29" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="G29" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="H29" s="10" t="n">
         <v>-4.5</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="I29" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="K29" s="10" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="M29" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="O29" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="Q29" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="7" t="n">
+      <c r="S29" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="7" t="n">
+      <c r="U29" s="10" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5742,24 +5860,25 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" s="7" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" s="7" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" s="7" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" s="10" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" s="10" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" s="10" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" s="10" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5777,24 +5896,25 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" s="7" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" s="7" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" s="10" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" s="10" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5812,24 +5932,25 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" s="7" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" s="7" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" s="7" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" s="10" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" s="10" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" s="10" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" s="10" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5847,24 +5968,29 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" s="7" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" s="7" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" s="7" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 전자기술 순강도 -16 최약, 광모듈·반도체 신저가 속출로 약세 추정</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" s="10" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5882,24 +6008,29 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" s="7" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" s="7" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" s="7" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 기술주 전반 약세, 광모듈·반도체 조정에 약세 추정</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" s="10" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" s="10" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" s="10" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" s="10" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5917,24 +6048,29 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" s="7" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" s="7" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 광통신·부품 약세 연동 추정(통신 순강도 중립)</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" s="10" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" s="10" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5952,24 +6088,29 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" s="7" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" s="7" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" s="7" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 소비내구재 순강도 +2 강세, 신에너지차 상대 견조 추정</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" s="10" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" s="10" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" s="10" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5987,24 +6128,29 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" s="7" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" s="7" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" s="7" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 제조업 breadth 약세, 방산 뚜렷한 촉매 없음 추정</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" s="10" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6022,24 +6168,29 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" s="7" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" s="7" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" s="7" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 신재생·제조 breadth 약세 추정</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr"/>
+      <c r="F38" s="10" t="inlineStr"/>
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" s="10" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" s="10" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" s="10" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6057,24 +6208,29 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" s="7" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" s="7" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" s="7" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 소비 중립, 방향성 부재 추정</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" s="10" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6092,24 +6248,29 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" s="7" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 금융 순강도 +9 최강, 은행 고배당 순환매로 신고가 다수 강세 추정</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" s="10" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" s="10" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" s="10" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6127,24 +6288,29 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" s="7" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" s="7" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" s="7" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 비철금속 순강도 -2 약세 추정</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="10" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr"/>
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" s="10" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" s="10" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6162,24 +6328,29 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="7" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" s="7" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" s="7" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 부동산 뚜렷한 촉매 없음 추정</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" s="10" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" s="10" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" s="10" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6197,24 +6368,29 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" s="7" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" s="7" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" s="7" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 금융 강세 흐름 일부 수혜 추정, 증권 개별 촉매 미확인</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" s="10" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" s="10" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6232,24 +6408,29 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="7" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" s="7" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" s="7" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 의약 중립, 방향성 부재 추정</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" s="10" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" s="10" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" s="10" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" s="10" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6267,24 +6448,29 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" s="7" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" s="7" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" s="7" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 소비 중립, 방어주 선호 일부 추정</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" s="10" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" s="10" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6294,7 +6480,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3.4"/>
@@ -6306,7 +6492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-11.8"/>
@@ -6318,7 +6504,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-22.3"/>
@@ -6330,7 +6516,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-21.8"/>
@@ -6342,7 +6528,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-8.9"/>
@@ -6354,7 +6540,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -6364,7 +6550,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -6374,7 +6560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-7.2"/>
@@ -6386,7 +6572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.6"/>
@@ -6398,7 +6584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-8.4"/>
@@ -6410,7 +6596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -6518,12 +6704,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6562,10 +6748,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -6611,10 +6801,10 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6660,15 +6850,15 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6713,15 +6903,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6760,10 +6950,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -6811,19 +7005,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>(전일) 스노우플레이크(클라우드 데이터플랫폼): 웰스파고 목표가 $320→$500 상향·AI에이전트 지출 가속 논거</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6864,15 +7058,15 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6913,15 +7107,19 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6962,10 +7160,10 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7011,15 +7209,15 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7060,15 +7258,15 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7113,15 +7311,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7164,10 +7362,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7213,15 +7415,15 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7262,10 +7464,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7315,10 +7521,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7364,15 +7570,15 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7417,15 +7623,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7470,15 +7680,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7519,10 +7733,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7568,19 +7782,19 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>(전일) (유전서비스): 실적 상회에도 에너지 섹터 약세·유가 불확실성으로 하락</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7625,10 +7839,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7678,10 +7892,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7727,15 +7941,15 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7776,15 +7990,15 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7825,15 +8039,15 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7876,10 +8090,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7929,10 +8147,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7982,15 +8200,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8031,15 +8249,15 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8078,10 +8296,14 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8131,10 +8353,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8178,10 +8400,10 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8231,10 +8453,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8280,15 +8506,15 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8333,15 +8559,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8380,15 +8606,15 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8427,10 +8653,10 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8478,10 +8704,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8531,14 +8761,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="M41" s="11" t="inlineStr">
         <is>
           <t>(전일) 레녹스인터내셔널(주거용 HVAC): 2Q매출 소폭 미달·FY EPS가이던스 $23.50으로 하향(컨센 -4.7%)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8584,10 +8814,10 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8635,15 +8865,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8684,10 +8918,10 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8737,14 +8971,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="M45" s="11" t="inlineStr">
         <is>
           <t>(전일) (캐주얼다이닝): 다수 증권사 목표가 상향(웰스파고 $220)·소고기값 완화 기대</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8790,19 +9024,19 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="M46" s="11" t="inlineStr">
         <is>
           <t>(전일) (산업용 바코드·모바일컴퓨터): 소프트웨어·AI분석 수요 회복 기대, 목표가 연속 상향으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8843,10 +9077,10 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8890,10 +9124,10 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8941,19 +9175,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M49" s="9" t="inlineStr">
-        <is>
-          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8998,10 +9232,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9049,19 +9287,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M51" s="9" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>(전일) 왓스코(HVAC유통): 2Q EPS $4.00 컨센 $4.39 미달·매출총이익률 27.5%로 전년比 축소</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9100,10 +9338,10 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9147,19 +9385,19 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="9" t="inlineStr">
+      <c r="M53" s="11" t="inlineStr">
         <is>
           <t>(전일) 에버코어(독립자문 투자은행): 2Q EPS 소폭 상회했으나 1Q 역대최고 대비 실망·'뉴스에 팔자'</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9200,15 +9438,15 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9253,15 +9491,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9306,10 +9544,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M56" s="9" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9359,15 +9597,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M57" s="9" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9408,15 +9646,15 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="9" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9455,10 +9693,10 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9508,10 +9746,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M60" s="9" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9561,7 +9799,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M61"/>
@@ -9661,7 +9899,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9707,10 +9945,10 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9754,15 +9992,15 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9803,10 +10041,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9856,10 +10098,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9909,10 +10151,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9958,10 +10200,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10007,10 +10249,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10056,10 +10298,14 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10105,14 +10351,14 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>(전일) (자동차부품 1위): 7/31 결산 앞둔 기대매수, 日증시 반등 수혜</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10158,14 +10404,14 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>(전일) (디스코·반도체 다이싱장비): 7-9월 순이익 가이던스 395억엔이 컨센 473억엔 대폭 하회로 -12% 급락</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10215,14 +10461,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>(전일) (브리지스톤·타이어): 1Q 경상이익 +47% 호조, 8/7 결산 기대 매수로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10268,19 +10514,19 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>(전일) (도쿄디즈니리조트): 입장권 상한 인상 보도·7/30 결산 기대로 연속 급등</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10321,10 +10567,14 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10370,14 +10620,14 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>(전일) 레이저테크(EUV 마스크검사장비): SK하이닉스 실적 미달+한국증시 서킷브레이커로 장비주 집중매도</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10423,14 +10673,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>(전일) 코나미그룹(게임·헬스클럽 복합): 카프콤 1Q 영업익 +67% 호실적에 게임주 전반 동반매수</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10476,14 +10726,14 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>(전일) (게임·완구): 맥쿼리 목표주가 5500→5600엔 상향, 8/5 결산 기대매수</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10529,14 +10779,14 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>(전일) (IT컨설팅·NRI): 7/30 결산 앞두고 기대 매수, FY27 이익 전망 개선으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10582,10 +10832,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10631,19 +10881,19 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>(전일) (레조낙·반도체소재): 중국 노광장비 자체제조 보도·아시아 AI반도체 전반 급락 수급으로 신저가</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10684,10 +10934,14 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10733,14 +10987,14 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>(전일) 스바루(자동차): AI반도체 섹터 급락에 저배당·저PBR 자동차주로 자금이동</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10786,14 +11040,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="11" t="inlineStr">
         <is>
           <t>(전일) (ERP·업무SW): 4-6월 순이익 16%↑ 결산 재평가, IT섹터로 자금 이동</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10837,10 +11091,10 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10890,14 +11144,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>(전일) 시마노(자전거 부품·낚시): 2Q 순익 +606% 급증 호실적에 상반기 업적 상방수정</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10943,10 +11197,10 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10992,15 +11246,15 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11045,15 +11299,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11094,15 +11352,19 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11143,7 +11405,11 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>마키타(전동공구): 1분기 이익 상회분 대부분 관세환급 일회성·실수요 부진·서유럽 -11%에 급락</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M30"/>
@@ -11243,7 +11509,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11293,14 +11559,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 독립 촉매 없이 은행 섹터 전반 강세·위안화 강세 수급으로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11350,10 +11616,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11403,10 +11673,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11452,10 +11722,10 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11501,14 +11771,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11558,14 +11828,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>(전일) (가전·로봇): 자사주 매입 집행·휴머노이드 상업화 기대 매수세 유입으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11609,14 +11879,14 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>(전일) (음식배달·로컬커머스): 미이란 긴장 완화 리스크오프 해소·과기주 매수, 2Q 적자축소 기대</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11662,19 +11932,19 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>(전일) (손해보험·중국재보험): 배당지급일 직전 막차 매수 집중, 은행·보험 방어섹터 동반 강세로 신고가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11717,10 +11987,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11766,14 +12040,14 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>(전일) 하이얼스마트홈(가전 제조): 신소비·대형소비주 섹터 수급 유입 동반 강세(개별 촉매 미확인, 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11823,15 +12097,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11872,10 +12146,14 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11921,14 +12199,14 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11976,14 +12254,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>(전일) 성훙테크H(AI서버 PCB): AI하드웨어 PCB 섹터 조정 지속·엔비디아 루빈 품질 루머 및 이익 정점 우려</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12029,14 +12307,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>(전일) 은하오락(마카오 카지노): 마카오 GGR 회복 기대·7월 일평균 매출 전주比 +9%·골드만 매수 유지</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12084,14 +12362,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>(전일) 딩타이가오커(PCB 드릴비트 글로벌 1위): AI서버 PCB 섹터 전반 급락(광허테크 등 -16%)에 동반</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12141,14 +12419,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>(전일) (복합기업·부동산): UBS 목표가 20% 상향, 태고지산·캐세이퍼시픽 이익 기여 기대로 신고가</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12198,19 +12476,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>(전일) 스와이어퍼시픽B(항공·부동산·음료 복합): 특별한 뉴스 없음(시장 전반 상승 흐름 동반 추정)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12249,10 +12527,14 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12302,14 +12584,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12355,14 +12637,14 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>(전일) 텐센트뮤직(온라인음악 스트리밍): 항셍테크 +2.84%, 텐센트·비리비리 등 대형 인터넷주 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12408,14 +12690,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="11" t="inlineStr">
         <is>
           <t>(전일) (동박적층판 PCB소재·젠타오): 엔비디아 차세대 AI서버랙 PCB 양산 2028년 연기 충격으로 -16% 급락</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12461,14 +12743,14 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>(전일) (국제택배·물류): 자사주 매입 지속, 동남아 패키지 처리량 +84% 역대 최대로 신고가</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12516,14 +12798,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>(전일) HKT트러스트(홍콩 통신): 7/30 중간 실적발표 앞두고 기대 매수 유입(+0.08% 소폭)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12573,19 +12855,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>(전일) (홍콩 국적 항공사): 캐세이퍼시픽, 상반기 순이익 60~65억 홍콩달러(전년비 최대 +76%) 예고, 여객·화물 호조</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12628,15 +12910,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12675,7 +12961,11 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M28"/>
@@ -12775,7 +13065,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12819,14 +13109,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 창업판 급락 속 방어주 순환매로 은행섹터 강세, 공상은행 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12870,14 +13160,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>(전일) 농업은행(국유 대형은행): 섹터 선두 강세 후 신고가권 유지, 월간 고배당·저PB 리레이팅 수급 유입</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12927,19 +13217,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>(전일) 젠서은행(국유 대형은행): 7/28 A주 역대 신고가·600억 2차자본채 발행 후 고배당 수급 지속, 신고가 보합</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12980,15 +13270,15 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13029,10 +13319,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13078,14 +13372,14 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>(전일) (우량 주식은행·자오상은행): 기술주 대피 자금이 고배당 은행주로 이동, 배당 매력에 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13131,10 +13425,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13184,19 +13478,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>(전일) (가전 대표주·메이디그룹): 이구환신 수혜 기대·기술섹터 폭락 반사 순환매로 신고가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13235,15 +13529,19 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13284,10 +13582,14 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13333,15 +13635,15 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13382,10 +13684,14 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13431,19 +13737,19 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>(전일) 둥산징미(PCB·광모듈): CPO·1.6T 광모듈 가격급락 루머+회사 단가하락 발언, CPO/PCB 연속 하한가권</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13484,10 +13790,14 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13531,14 +13841,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>(전일) (국산 GPU·무어스레드): AI 하드웨어 섹터 전반 폭락 속 고평가 국산 GPU주 동반 급락</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13584,10 +13894,10 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13633,19 +13943,19 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>(전일) 거리전기(에어컨 제조): AI·반도체주 급락 속 대소비재 역방향 강세, 이구환신(가전 교체보조) 확대 기대</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13686,10 +13996,14 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13735,10 +14049,10 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13784,10 +14098,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13833,10 +14147,10 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13882,14 +14196,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="11" t="inlineStr">
         <is>
           <t>(전일) (가전 대형주·하이얼스마트홈): 이구환신 정책 수혜·기술주 급락 반사 방어주 순환매로 신고가</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13939,14 +14253,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>(전일) 성훙커지A(PCB): 둥산징미 등 CPO 섹터 연속 급락 여파로 PCB 개념주 동반 하락, 섹터 수급 이탈</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13992,19 +14306,19 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14047,10 +14361,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14096,19 +14414,19 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M27" s="11" t="inlineStr">
         <is>
           <t>(전일) 중궈중처(철도차량 제조): 2Q 신규수주 516억위안(2025매출 18.9%) 모멘텀 지속, 대소비재 강세 속 신고가</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14149,10 +14467,14 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14198,19 +14520,19 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="M29" s="11" t="inlineStr">
         <is>
           <t>(전일) (광섬유 제조·창페이광섬유): 6월 고점 이후 광통신 섹터 조정 지속, 신규 촉매 없이 약세 연장</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14251,10 +14573,14 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14300,14 +14626,14 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="11" t="inlineStr">
         <is>
           <t>(전일) (광섬유 광케이블·헝퉁광전): AI 연산 수요 불확실·한국 광통신주 동반 하락으로 급락</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14353,15 +14679,15 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14400,10 +14726,10 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14447,19 +14773,19 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr">
-        <is>
-          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14500,10 +14826,10 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14549,10 +14875,10 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14598,10 +14924,10 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14645,10 +14971,10 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14694,15 +15020,15 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14743,10 +15069,10 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14796,10 +15122,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14845,14 +15171,14 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14900,14 +15226,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="M43" s="11" t="inlineStr">
         <is>
           <t>(전일) (우주·특수전원): 상장 초 급등 후 조정 지속, 신규 재료 없음(IPO 거품 해소)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14953,10 +15279,10 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15002,19 +15328,19 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="M45" s="11" t="inlineStr">
         <is>
           <t>(전일) 중차이커지(유리섬유·AI전자포): 유상증자(44.8억위안) 희석 우려+AI하드웨어 조정 지속, 과창50 -4% 여파 신저가</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15055,15 +15381,15 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15102,10 +15428,14 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15151,7 +15481,7 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M48"/>

--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$I$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$M$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$M$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$M$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$M$48</definedName>
   </definedNames>
@@ -550,7 +550,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PER(TTM중앙값)</t>
+          <t>PER(12MF중앙값)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="I2" t="n">
         <v>2.3</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>31.9</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>5.5</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>25.8</v>
+        <v>21.5</v>
       </c>
       <c r="I4" t="n">
         <v>4.6</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>20.7</v>
+        <v>15.9</v>
       </c>
       <c r="I5" t="n">
         <v>2.5</v>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22.9</v>
+        <v>16.9</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>34.3</v>
+        <v>22.7</v>
       </c>
       <c r="I7" t="n">
         <v>6.6</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="I8" t="n">
         <v>2.2</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23</v>
+        <v>16.6</v>
       </c>
       <c r="I9" t="n">
         <v>3.3</v>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>43.1</v>
+        <v>28.8</v>
       </c>
       <c r="I10" t="n">
         <v>7.9</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26.6</v>
+        <v>23.3</v>
       </c>
       <c r="I11" t="n">
         <v>5.3</v>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="I12" t="n">
         <v>2.9</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>26.1</v>
+        <v>20.1</v>
       </c>
       <c r="I13" t="n">
         <v>8.4</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>28.3</v>
+        <v>21.3</v>
       </c>
       <c r="I14" t="n">
         <v>4.4</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>33.5</v>
+        <v>23.9</v>
       </c>
       <c r="I15" t="n">
         <v>5.7</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>32.7</v>
+        <v>19.8</v>
       </c>
       <c r="I16" t="n">
         <v>5.6</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="I17" t="n">
         <v>3.3</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>24.6</v>
+        <v>19.6</v>
       </c>
       <c r="I18" t="n">
         <v>5.1</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>17.4</v>
+        <v>9.9</v>
       </c>
       <c r="I19" t="n">
         <v>2.1</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>54</v>
+        <v>30.5</v>
       </c>
       <c r="I20" t="n">
         <v>9.6</v>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31.1</v>
+        <v>15.7</v>
       </c>
       <c r="I21" t="n">
         <v>2.5</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>25.8</v>
+        <v>21.5</v>
       </c>
       <c r="I22" t="n">
         <v>4.1</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>16.7</v>
+        <v>14.5</v>
       </c>
       <c r="I23" t="n">
         <v>1.4</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>37.1</v>
+        <v>31.6</v>
       </c>
       <c r="I24" t="n">
         <v>4.6</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>30.3</v>
+        <v>25.3</v>
       </c>
       <c r="I25" t="n">
         <v>3.7</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>26.1</v>
+        <v>30.5</v>
       </c>
       <c r="I26" t="n">
         <v>2.9</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26.5</v>
+        <v>19.9</v>
       </c>
       <c r="I27" t="n">
         <v>3.3</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="I28" t="n">
         <v>0.8</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>38.9</v>
+        <v>30.6</v>
       </c>
       <c r="I29" t="n">
         <v>4.3</v>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>29.6</v>
+        <v>13.2</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="31">
@@ -2063,11 +2063,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2098,11 +2098,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>11.6</v>
+        <v>15.4</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="33">
@@ -2133,31 +2133,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-1</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>25.6</v>
+        <v>12.7</v>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="34">
@@ -2168,31 +2168,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>혼조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14.6</v>
+        <v>24.4</v>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="35">
@@ -2203,28 +2203,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>혼조</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>18.9</v>
+        <v>17.9</v>
       </c>
       <c r="I35" t="n">
         <v>1.9</v>
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="37">
@@ -2273,11 +2273,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>20.6</v>
+        <v>14.3</v>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>13.4</v>
+        <v>20.3</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="40">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7.8</v>
+        <v>11.4</v>
       </c>
       <c r="I40" t="n">
         <v>0.7</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>13.1</v>
+        <v>18.1</v>
       </c>
       <c r="I41" t="n">
         <v>2.5</v>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19.2</v>
+        <v>12.3</v>
       </c>
       <c r="I42" t="n">
         <v>2.3</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>16.9</v>
+        <v>13.7</v>
       </c>
       <c r="I43" t="n">
         <v>3.3</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>13.8</v>
+        <v>11.3</v>
       </c>
       <c r="I44" t="n">
         <v>1.6</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12.6</v>
+        <v>10.3</v>
       </c>
       <c r="I45" t="n">
         <v>0.8</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>16.6</v>
+        <v>14.9</v>
       </c>
       <c r="I46" t="n">
         <v>5.7</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="I47" t="n">
         <v>1.2</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>22.3</v>
+        <v>13.8</v>
       </c>
       <c r="I48" t="n">
         <v>2.5</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>56.6</v>
+        <v>17.2</v>
       </c>
       <c r="I49" t="n">
         <v>4.2</v>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="I51" t="n">
         <v>3.4</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>11.9</v>
+        <v>7</v>
       </c>
       <c r="I52" t="n">
         <v>1.1</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>34.4</v>
+        <v>32.6</v>
       </c>
       <c r="I53" t="n">
         <v>5.1</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="I54" t="n">
         <v>0.2</v>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>14.6</v>
+        <v>8.5</v>
       </c>
       <c r="I55" t="n">
         <v>3.2</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>22.5</v>
+        <v>13.5</v>
       </c>
       <c r="I56" t="n">
         <v>1.6</v>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>21.5</v>
+        <v>12</v>
       </c>
       <c r="I57" t="n">
         <v>1.7</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I58" t="n">
         <v>0.9</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>16.5</v>
+        <v>20.8</v>
       </c>
       <c r="I59" t="n">
         <v>2.9</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>16.8</v>
+        <v>10.4</v>
       </c>
       <c r="I60" t="n">
         <v>1.7</v>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20.8</v>
+        <v>19.6</v>
       </c>
       <c r="I61" t="n">
         <v>1.7</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>25.4</v>
+        <v>9.1</v>
       </c>
       <c r="I63" t="n">
         <v>3.3</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>16.9</v>
+        <v>12.2</v>
       </c>
       <c r="I64" t="n">
         <v>2.9</v>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>50.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>7.7</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>32.2</v>
+        <v>29.2</v>
       </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="67">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>57.6</v>
+        <v>30.3</v>
       </c>
       <c r="I67" t="n">
         <v>9</v>
@@ -3376,9 +3376,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H68" t="n">
-        <v>17.3</v>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>1.4</v>
       </c>
@@ -3411,9 +3409,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>3.9</v>
       </c>
@@ -3446,9 +3442,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>2.8</v>
       </c>
@@ -3482,7 +3476,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>14.8</v>
+        <v>12.1</v>
       </c>
       <c r="I71" t="n">
         <v>1.9</v>
@@ -3517,7 +3511,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="I72" t="n">
         <v>3.7</v>
@@ -3552,7 +3546,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>43.7</v>
+        <v>30.1</v>
       </c>
       <c r="I73" t="n">
         <v>4.9</v>
@@ -3586,9 +3580,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>0.4</v>
       </c>
@@ -3629,7 +3621,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>※ PER=TTM 순이익, PBR=최근분기 순자산 — 섹터 유니버스($10B+) 중앙값, 적자 제외</t>
+          <t>※ PER=12개월 선행(12MF, 컨센서스 기준), PBR=최근분기 순자산 — 섹터 유니버스($10B+) 중앙값, 적자 제외</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6621,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
@@ -6679,7 +6671,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>PER(TTM)</t>
+          <t>PER(12MF)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -6739,7 +6731,7 @@
         <v>1368.3</v>
       </c>
       <c r="I2" t="n">
-        <v>20.3</v>
+        <v>17.4</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -6748,11 +6740,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="11" t="inlineStr">
-        <is>
-          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
-        </is>
-      </c>
+      <c r="M2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -6790,7 +6778,7 @@
         <v>510.1</v>
       </c>
       <c r="I3" t="n">
-        <v>33.4</v>
+        <v>27.3</v>
       </c>
       <c r="J3" t="n">
         <v>76.2</v>
@@ -6839,7 +6827,7 @@
         <v>159.8</v>
       </c>
       <c r="I4" t="n">
-        <v>17.5</v>
+        <v>15.9</v>
       </c>
       <c r="J4" t="n">
         <v>5.8</v>
@@ -6888,7 +6876,7 @@
         <v>132.4</v>
       </c>
       <c r="I5" t="n">
-        <v>18.2</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
         <v>6.6</v>
@@ -6941,7 +6929,7 @@
         <v>113.5</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2</v>
+        <v>11.7</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -6950,11 +6938,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
-        </is>
-      </c>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6991,7 +6975,9 @@
       <c r="H7" t="n">
         <v>103.3</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>140.1</v>
+      </c>
       <c r="J7" t="n">
         <v>53.3</v>
       </c>
@@ -7047,7 +7033,7 @@
         <v>94</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>33.9</v>
       </c>
       <c r="J8" t="n">
         <v>15</v>
@@ -7096,7 +7082,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>13.2</v>
       </c>
       <c r="J9" t="n">
         <v>2.5</v>
@@ -7107,11 +7093,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
-        </is>
-      </c>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7149,7 +7131,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>28.5</v>
+        <v>32</v>
       </c>
       <c r="J10" t="n">
         <v>11</v>
@@ -7198,7 +7180,7 @@
         <v>65.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4</v>
+        <v>18.2</v>
       </c>
       <c r="J11" t="n">
         <v>2.8</v>
@@ -7247,7 +7229,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>17.8</v>
+        <v>15.3</v>
       </c>
       <c r="J12" t="n">
         <v>2.8</v>
@@ -7296,7 +7278,7 @@
         <v>52.9</v>
       </c>
       <c r="I13" t="n">
-        <v>59.9</v>
+        <v>23.8</v>
       </c>
       <c r="J13" t="n">
         <v>7.8</v>
@@ -7349,7 +7331,7 @@
         <v>50.7</v>
       </c>
       <c r="I14" t="n">
-        <v>27.5</v>
+        <v>22</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -7362,11 +7344,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
-        </is>
-      </c>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -7404,7 +7382,7 @@
         <v>50.6</v>
       </c>
       <c r="I15" t="n">
-        <v>43.3</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
@@ -7453,7 +7431,7 @@
         <v>49.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.5</v>
+        <v>30.4</v>
       </c>
       <c r="J16" t="n">
         <v>22.2</v>
@@ -7464,11 +7442,7 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -7506,7 +7480,7 @@
         <v>38.7</v>
       </c>
       <c r="I17" t="n">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -7559,7 +7533,7 @@
         <v>31.7</v>
       </c>
       <c r="I18" t="n">
-        <v>19.7</v>
+        <v>16.2</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -7608,7 +7582,7 @@
         <v>31</v>
       </c>
       <c r="I19" t="n">
-        <v>37.2</v>
+        <v>36.8</v>
       </c>
       <c r="J19" t="n">
         <v>11.6</v>
@@ -7623,11 +7597,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -7665,7 +7635,7 @@
         <v>27.4</v>
       </c>
       <c r="I20" t="n">
-        <v>48.8</v>
+        <v>22.4</v>
       </c>
       <c r="J20" t="n">
         <v>25.5</v>
@@ -7680,11 +7650,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
-        </is>
-      </c>
+      <c r="M20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -7722,7 +7688,7 @@
         <v>26.7</v>
       </c>
       <c r="I21" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="J21" t="n">
         <v>2.3</v>
@@ -7771,7 +7737,7 @@
         <v>26.4</v>
       </c>
       <c r="I22" t="n">
-        <v>16.6</v>
+        <v>12.4</v>
       </c>
       <c r="J22" t="n">
         <v>2.4</v>
@@ -7824,7 +7790,7 @@
         <v>25.9</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>16.9</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -7877,7 +7843,7 @@
         <v>23.1</v>
       </c>
       <c r="I24" t="n">
-        <v>32.9</v>
+        <v>25.8</v>
       </c>
       <c r="J24" t="n">
         <v>8.4</v>
@@ -7930,7 +7896,7 @@
         <v>21.6</v>
       </c>
       <c r="I25" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="J25" t="n">
         <v>2.2</v>
@@ -7979,7 +7945,7 @@
         <v>20.4</v>
       </c>
       <c r="I26" t="n">
-        <v>20.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>1.2</v>
@@ -8028,7 +7994,7 @@
         <v>20.3</v>
       </c>
       <c r="I27" t="n">
-        <v>43</v>
+        <v>19.9</v>
       </c>
       <c r="J27" t="n">
         <v>50.2</v>
@@ -8076,7 +8042,9 @@
       <c r="H28" t="n">
         <v>20.1</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>77.09999999999999</v>
+      </c>
       <c r="J28" t="n">
         <v>4.6</v>
       </c>
@@ -8090,11 +8058,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
-        </is>
-      </c>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -8132,7 +8096,7 @@
         <v>19.5</v>
       </c>
       <c r="I29" t="n">
-        <v>57.8</v>
+        <v>92.3</v>
       </c>
       <c r="J29" t="n">
         <v>4.2</v>
@@ -8185,7 +8149,7 @@
         <v>18.7</v>
       </c>
       <c r="I30" t="n">
-        <v>28.5</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
         <v>5.5</v>
@@ -8238,7 +8202,7 @@
         <v>17.9</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>13.3</v>
       </c>
       <c r="J31" t="n">
         <v>3.2</v>
@@ -8287,7 +8251,7 @@
         <v>17.3</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>21.3</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -8296,11 +8260,7 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
-        </is>
-      </c>
+      <c r="M32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -8338,7 +8298,7 @@
         <v>17.2</v>
       </c>
       <c r="I33" t="n">
-        <v>17.1</v>
+        <v>25.2</v>
       </c>
       <c r="J33" t="n">
         <v>2.5</v>
@@ -8390,7 +8350,9 @@
       <c r="H34" t="n">
         <v>17.1</v>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>21.5</v>
+      </c>
       <c r="J34" t="n">
         <v>4.9</v>
       </c>
@@ -8438,7 +8400,7 @@
         <v>16.8</v>
       </c>
       <c r="I35" t="n">
-        <v>19.4</v>
+        <v>14.8</v>
       </c>
       <c r="J35" t="n">
         <v>2.3</v>
@@ -8453,11 +8415,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
-        </is>
-      </c>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -8495,7 +8453,7 @@
         <v>15</v>
       </c>
       <c r="I36" t="n">
-        <v>16.4</v>
+        <v>13.1</v>
       </c>
       <c r="J36" t="n">
         <v>1.9</v>
@@ -8544,7 +8502,7 @@
         <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>25.7</v>
       </c>
       <c r="J37" t="n">
         <v>2.8</v>
@@ -8596,7 +8554,9 @@
       <c r="H38" t="n">
         <v>14.9</v>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>63.5</v>
+      </c>
       <c r="J38" t="n">
         <v>2.9</v>
       </c>
@@ -8690,7 +8650,9 @@
       <c r="H40" t="n">
         <v>14.6</v>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>24.4</v>
+      </c>
       <c r="J40" t="n">
         <v>1316.2</v>
       </c>
@@ -8704,11 +8666,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr">
-        <is>
-          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
-        </is>
-      </c>
+      <c r="M40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8746,7 +8704,7 @@
         <v>14.5</v>
       </c>
       <c r="I41" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="J41" t="n">
         <v>11.1</v>
@@ -8803,7 +8761,7 @@
         <v>14</v>
       </c>
       <c r="I42" t="n">
-        <v>30.3</v>
+        <v>27.7</v>
       </c>
       <c r="J42" t="n">
         <v>2.9</v>
@@ -8851,7 +8809,9 @@
       <c r="H43" t="n">
         <v>13.8</v>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>13</v>
+      </c>
       <c r="J43" t="n">
         <v>2.3</v>
       </c>
@@ -8865,11 +8825,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr">
-        <is>
-          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8907,7 +8863,7 @@
         <v>13.7</v>
       </c>
       <c r="I44" t="n">
-        <v>25.8</v>
+        <v>21.5</v>
       </c>
       <c r="J44" t="n">
         <v>9.1</v>
@@ -8956,7 +8912,7 @@
         <v>13.7</v>
       </c>
       <c r="I45" t="n">
-        <v>33.3</v>
+        <v>30.9</v>
       </c>
       <c r="J45" t="n">
         <v>9</v>
@@ -9013,7 +8969,7 @@
         <v>13.7</v>
       </c>
       <c r="I46" t="n">
-        <v>34.9</v>
+        <v>15.3</v>
       </c>
       <c r="J46" t="n">
         <v>4</v>
@@ -9066,7 +9022,7 @@
         <v>13.4</v>
       </c>
       <c r="I47" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="J47" t="n">
         <v>5.8</v>
@@ -9114,7 +9070,9 @@
       <c r="H48" t="n">
         <v>13.2</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>24.4</v>
+      </c>
       <c r="J48" t="n">
         <v>2</v>
       </c>
@@ -9162,7 +9120,7 @@
         <v>13</v>
       </c>
       <c r="I49" t="n">
-        <v>27.6</v>
+        <v>25.3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -9177,7 +9135,7 @@
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
+          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9175,7 @@
         <v>12.7</v>
       </c>
       <c r="I50" t="n">
-        <v>282.6</v>
+        <v>32.4</v>
       </c>
       <c r="J50" t="n">
         <v>18.1</v>
@@ -9232,11 +9190,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
-        </is>
-      </c>
+      <c r="M50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -9274,7 +9228,7 @@
         <v>12.6</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>24.7</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -9376,7 +9330,7 @@
         <v>12.1</v>
       </c>
       <c r="I53" t="n">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -9427,7 +9381,7 @@
         <v>11.9</v>
       </c>
       <c r="I54" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="J54" t="n">
         <v>2.5</v>
@@ -9476,7 +9430,7 @@
         <v>11.8</v>
       </c>
       <c r="I55" t="n">
-        <v>22.3</v>
+        <v>19.6</v>
       </c>
       <c r="J55" t="n">
         <v>7.6</v>
@@ -9529,7 +9483,7 @@
         <v>11.2</v>
       </c>
       <c r="I56" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="J56" t="n">
         <v>1.7</v>
@@ -9582,7 +9536,7 @@
         <v>11.1</v>
       </c>
       <c r="I57" t="n">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="J57" t="n">
         <v>1.4</v>
@@ -9635,7 +9589,7 @@
         <v>11</v>
       </c>
       <c r="I58" t="n">
-        <v>33.9</v>
+        <v>18.9</v>
       </c>
       <c r="J58" t="n">
         <v>4</v>
@@ -9684,7 +9638,7 @@
         <v>10.3</v>
       </c>
       <c r="I59" t="n">
-        <v>73.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -9731,7 +9685,7 @@
         <v>10.3</v>
       </c>
       <c r="I60" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="J60" t="n">
         <v>2.3</v>
@@ -9784,7 +9738,7 @@
         <v>10.1</v>
       </c>
       <c r="I61" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="J61" t="n">
         <v>4</v>
@@ -9813,7 +9767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9824,7 +9778,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
@@ -9874,7 +9828,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>PER(TTM)</t>
+          <t>PER(12MF)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -9931,10 +9885,10 @@
         <v>-2.51</v>
       </c>
       <c r="H2" t="n">
-        <v>169.4</v>
+        <v>169.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>42.5</v>
       </c>
       <c r="J2" t="n">
         <v>1.5</v>
@@ -9980,9 +9934,11 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>141.3</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>141.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="J3" t="n">
         <v>2.9</v>
       </c>
@@ -10027,10 +9983,10 @@
         <v>2.92</v>
       </c>
       <c r="H4" t="n">
-        <v>131.7</v>
+        <v>131.8</v>
       </c>
       <c r="I4" t="n">
-        <v>39.2</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>15.4</v>
@@ -10041,11 +9997,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
-        </is>
-      </c>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -10080,10 +10032,10 @@
         <v>-1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>111.3</v>
+        <v>111.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.2</v>
+        <v>29.7</v>
       </c>
       <c r="J5" t="n">
         <v>11.4</v>
@@ -10136,7 +10088,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="J6" t="n">
         <v>2.3</v>
@@ -10186,10 +10138,10 @@
         <v>1.99</v>
       </c>
       <c r="H7" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="I7" t="n">
-        <v>22.3</v>
+        <v>25.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -10235,11 +10187,9 @@
         <v>1.51</v>
       </c>
       <c r="H8" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15.4</v>
-      </c>
+        <v>41.8</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>3.3</v>
       </c>
@@ -10286,9 +10236,7 @@
       <c r="H9" t="n">
         <v>39.2</v>
       </c>
-      <c r="I9" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>3</v>
       </c>
@@ -10298,11 +10246,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
-        </is>
-      </c>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -10340,7 +10284,7 @@
         <v>38.1</v>
       </c>
       <c r="I10" t="n">
-        <v>13.4</v>
+        <v>14.2</v>
       </c>
       <c r="J10" t="n">
         <v>1.1</v>
@@ -10393,7 +10337,7 @@
         <v>34.9</v>
       </c>
       <c r="I11" t="n">
-        <v>38.7</v>
+        <v>28.1</v>
       </c>
       <c r="J11" t="n">
         <v>9.699999999999999</v>
@@ -10445,9 +10389,7 @@
       <c r="H12" t="n">
         <v>32.6</v>
       </c>
-      <c r="I12" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>1.4</v>
       </c>
@@ -10502,9 +10444,7 @@
       <c r="H13" t="n">
         <v>31.1</v>
       </c>
-      <c r="I13" t="n">
-        <v>39.3</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>4.4</v>
       </c>
@@ -10556,7 +10496,7 @@
         <v>19.9</v>
       </c>
       <c r="I14" t="n">
-        <v>29.6</v>
+        <v>19.2</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
@@ -10567,11 +10507,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
-        </is>
-      </c>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -10609,7 +10545,7 @@
         <v>19.4</v>
       </c>
       <c r="I15" t="n">
-        <v>34.1</v>
+        <v>30.6</v>
       </c>
       <c r="J15" t="n">
         <v>13.4</v>
@@ -10662,7 +10598,7 @@
         <v>19.3</v>
       </c>
       <c r="I16" t="n">
-        <v>29.6</v>
+        <v>21.5</v>
       </c>
       <c r="J16" t="n">
         <v>5.2</v>
@@ -10715,7 +10651,7 @@
         <v>19.1</v>
       </c>
       <c r="I17" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -10765,11 +10701,9 @@
         <v>1.51</v>
       </c>
       <c r="H18" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>207.2</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>7.4</v>
       </c>
@@ -10818,10 +10752,10 @@
         <v>-0.65</v>
       </c>
       <c r="H19" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="J19" t="n">
         <v>0.8</v>
@@ -10869,9 +10803,7 @@
       <c r="H20" t="n">
         <v>14.4</v>
       </c>
-      <c r="I20" t="n">
-        <v>64.40000000000001</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>3.1</v>
       </c>
@@ -10922,9 +10854,7 @@
       <c r="H21" t="n">
         <v>13.3</v>
       </c>
-      <c r="I21" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>0.6</v>
       </c>
@@ -10934,11 +10864,7 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
-        </is>
-      </c>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -10976,7 +10902,7 @@
         <v>12.8</v>
       </c>
       <c r="I22" t="n">
-        <v>22.7</v>
+        <v>9.9</v>
       </c>
       <c r="J22" t="n">
         <v>0.7</v>
@@ -11028,9 +10954,7 @@
       <c r="H23" t="n">
         <v>12.7</v>
       </c>
-      <c r="I23" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>4.1</v>
       </c>
@@ -11129,7 +11053,7 @@
         <v>11.4</v>
       </c>
       <c r="I25" t="n">
-        <v>31.2</v>
+        <v>34.3</v>
       </c>
       <c r="J25" t="n">
         <v>2</v>
@@ -11186,7 +11110,7 @@
         <v>11.3</v>
       </c>
       <c r="I26" t="n">
-        <v>10.8</v>
+        <v>11.7</v>
       </c>
       <c r="J26" t="n">
         <v>0.8</v>
@@ -11235,7 +11159,7 @@
         <v>10.7</v>
       </c>
       <c r="I27" t="n">
-        <v>30.3</v>
+        <v>25.3</v>
       </c>
       <c r="J27" t="n">
         <v>10.5</v>
@@ -11284,7 +11208,7 @@
         <v>10.6</v>
       </c>
       <c r="I28" t="n">
-        <v>26.1</v>
+        <v>25.6</v>
       </c>
       <c r="J28" t="n">
         <v>2.8</v>
@@ -11299,11 +11223,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
-        </is>
-      </c>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -11341,7 +11261,7 @@
         <v>10.2</v>
       </c>
       <c r="I29" t="n">
-        <v>34.9</v>
+        <v>31.6</v>
       </c>
       <c r="J29" t="n">
         <v>4.9</v>
@@ -11352,11 +11272,7 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
-        </is>
-      </c>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -11394,7 +11310,7 @@
         <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="J30" t="n">
         <v>1.4</v>
@@ -11405,14 +11321,57 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>마키타(전동공구): 1분기 이익 상회분 대부분 관세환급 일회성·실수요 부진·서유럽 -11%에 급락</t>
-        </is>
-      </c>
+      <c r="M30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1803 JP Equity</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Shimizu Corporation</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Industrial Services</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2317.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M30"/>
+  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11434,7 +11393,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
@@ -11484,7 +11443,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>PER(TTM)</t>
+          <t>PER(12MF)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -11543,9 +11502,7 @@
       <c r="H2" t="n">
         <v>399.6</v>
       </c>
-      <c r="I2" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>0.6</v>
       </c>
@@ -11600,9 +11557,7 @@
       <c r="H3" t="n">
         <v>351.8</v>
       </c>
-      <c r="I3" t="n">
-        <v>7</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>0.7</v>
       </c>
@@ -11616,11 +11571,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
-        </is>
-      </c>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -11657,9 +11608,7 @@
       <c r="H4" t="n">
         <v>315.6</v>
       </c>
-      <c r="I4" t="n">
-        <v>6.3</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
@@ -11710,9 +11659,7 @@
       <c r="H5" t="n">
         <v>150.4</v>
       </c>
-      <c r="I5" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>1</v>
       </c>
@@ -11760,7 +11707,7 @@
         <v>100.8</v>
       </c>
       <c r="I6" t="n">
-        <v>89.40000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="J6" t="n">
         <v>2.9</v>
@@ -11773,7 +11720,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
+          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
         </is>
       </c>
     </row>
@@ -11812,9 +11759,7 @@
       <c r="H7" t="n">
         <v>96.3</v>
       </c>
-      <c r="I7" t="n">
-        <v>15.5</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>2.9</v>
       </c>
@@ -11869,7 +11814,9 @@
       <c r="H8" t="n">
         <v>72.7</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>87.09999999999999</v>
+      </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
@@ -11921,7 +11868,7 @@
         <v>47.3</v>
       </c>
       <c r="I9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="J9" t="n">
         <v>1.2</v>
@@ -11987,11 +11934,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
-        </is>
-      </c>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -12028,9 +11971,7 @@
       <c r="H11" t="n">
         <v>29.5</v>
       </c>
-      <c r="I11" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>1.5</v>
       </c>
@@ -12082,7 +12023,7 @@
         <v>25.1</v>
       </c>
       <c r="I12" t="n">
-        <v>18.9</v>
+        <v>16.2</v>
       </c>
       <c r="J12" t="n">
         <v>1.8</v>
@@ -12135,7 +12076,7 @@
         <v>22.5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.3</v>
@@ -12146,11 +12087,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
-        </is>
-      </c>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -12188,7 +12125,7 @@
         <v>22.4</v>
       </c>
       <c r="I14" t="n">
-        <v>56.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>4.7</v>
@@ -12201,7 +12138,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
+          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12177,9 @@
       <c r="H15" t="n">
         <v>22.3</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>12.2</v>
+      </c>
       <c r="J15" t="n">
         <v>7.4</v>
       </c>
@@ -12296,7 +12235,7 @@
         <v>19.2</v>
       </c>
       <c r="I16" t="n">
-        <v>14.1</v>
+        <v>12.9</v>
       </c>
       <c r="J16" t="n">
         <v>1.8</v>
@@ -12404,7 +12343,7 @@
         <v>15.3</v>
       </c>
       <c r="I18" t="n">
-        <v>47</v>
+        <v>12.3</v>
       </c>
       <c r="J18" t="n">
         <v>0.5</v>
@@ -12461,7 +12400,7 @@
         <v>15.3</v>
       </c>
       <c r="I19" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="J19" t="n">
         <v>0.1</v>
@@ -12527,11 +12466,7 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
-        </is>
-      </c>
+      <c r="M20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -12568,9 +12503,7 @@
       <c r="H21" t="n">
         <v>15.1</v>
       </c>
-      <c r="I21" t="n">
-        <v>33.7</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>3.2</v>
       </c>
@@ -12586,7 +12519,7 @@
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
+          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12559,7 @@
         <v>14</v>
       </c>
       <c r="I22" t="n">
-        <v>12.1</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>1.3</v>
@@ -12679,7 +12612,7 @@
         <v>12.7</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>11.3</v>
       </c>
       <c r="J23" t="n">
         <v>5.6</v>
@@ -12732,7 +12665,7 @@
         <v>12.6</v>
       </c>
       <c r="I24" t="n">
-        <v>60.8</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
@@ -12784,9 +12717,7 @@
       <c r="H25" t="n">
         <v>12.4</v>
       </c>
-      <c r="I25" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -12840,7 +12771,7 @@
         <v>11.5</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>1.6</v>
@@ -12910,11 +12841,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
-        </is>
-      </c>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -12951,7 +12878,9 @@
       <c r="H28" t="n">
         <v>10.1</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>12.2</v>
+      </c>
       <c r="J28" t="n">
         <v>0.4</v>
       </c>
@@ -12961,11 +12890,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M28"/>
@@ -12990,7 +12915,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
@@ -13040,7 +12965,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>PER(TTM)</t>
+          <t>PER(12MF)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -13097,7 +13022,7 @@
         <v>2.52</v>
       </c>
       <c r="H2" t="n">
-        <v>401.1</v>
+        <v>399.7</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
@@ -13148,7 +13073,7 @@
         <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>353.1</v>
+        <v>351.9</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
@@ -13199,11 +13124,9 @@
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>316.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>315.7</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0.8</v>
       </c>
@@ -13256,10 +13179,10 @@
         <v>-6.84</v>
       </c>
       <c r="H5" t="n">
-        <v>168.7</v>
+        <v>168.2</v>
       </c>
       <c r="I5" t="n">
-        <v>26.2</v>
+        <v>15.7</v>
       </c>
       <c r="J5" t="n">
         <v>6.1</v>
@@ -13305,10 +13228,10 @@
         <v>-9.15</v>
       </c>
       <c r="H6" t="n">
-        <v>158</v>
+        <v>157.5</v>
       </c>
       <c r="I6" t="n">
-        <v>64.3</v>
+        <v>21.9</v>
       </c>
       <c r="J6" t="n">
         <v>27</v>
@@ -13319,11 +13242,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
-        </is>
-      </c>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -13358,11 +13277,9 @@
         <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>151</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6.8</v>
-      </c>
+        <v>150.5</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>0.9</v>
       </c>
@@ -13411,10 +13328,10 @@
         <v>-9.109999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>106.9</v>
+        <v>106.5</v>
       </c>
       <c r="I8" t="n">
-        <v>242.7</v>
+        <v>91</v>
       </c>
       <c r="J8" t="n">
         <v>50.9</v>
@@ -13460,11 +13377,9 @@
         <v>2.23</v>
       </c>
       <c r="H9" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>15.4</v>
-      </c>
+        <v>96.3</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>2.9</v>
       </c>
@@ -13517,7 +13432,7 @@
         <v>3.24</v>
       </c>
       <c r="H10" t="n">
-        <v>92.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
@@ -13529,11 +13444,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
-        </is>
-      </c>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -13568,10 +13479,10 @@
         <v>-11.89</v>
       </c>
       <c r="H11" t="n">
-        <v>87.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I11" t="n">
-        <v>48.1</v>
+        <v>19.5</v>
       </c>
       <c r="J11" t="n">
         <v>25.3</v>
@@ -13582,11 +13493,7 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
-        </is>
-      </c>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -13621,11 +13528,9 @@
         <v>1.95</v>
       </c>
       <c r="H12" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7.1</v>
-      </c>
+        <v>63.6</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>0.6</v>
       </c>
@@ -13670,10 +13575,10 @@
         <v>2.74</v>
       </c>
       <c r="H13" t="n">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
@@ -13684,11 +13589,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
-        </is>
-      </c>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -13723,10 +13624,10 @@
         <v>-10</v>
       </c>
       <c r="H14" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I14" t="n">
-        <v>144.4</v>
+        <v>28.9</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -13776,11 +13677,9 @@
         <v>4.63</v>
       </c>
       <c r="H15" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6.8</v>
-      </c>
+        <v>45.7</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>0.4</v>
       </c>
@@ -13790,11 +13689,7 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
-        </is>
-      </c>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -13829,7 +13724,7 @@
         <v>-4.35</v>
       </c>
       <c r="H16" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
@@ -13880,10 +13775,10 @@
         <v>0.96</v>
       </c>
       <c r="H17" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="I17" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -13929,11 +13824,9 @@
         <v>1.97</v>
       </c>
       <c r="H18" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8.1</v>
-      </c>
+        <v>32.8</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>1.6</v>
       </c>
@@ -13982,10 +13875,10 @@
         <v>2.93</v>
       </c>
       <c r="H19" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="I19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
@@ -13996,11 +13889,7 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
-        </is>
-      </c>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -14035,10 +13924,10 @@
         <v>-9.970000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="I20" t="n">
-        <v>52.2</v>
+        <v>34.3</v>
       </c>
       <c r="J20" t="n">
         <v>10.5</v>
@@ -14084,10 +13973,10 @@
         <v>-8.27</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="I21" t="n">
-        <v>43.6</v>
+        <v>24.4</v>
       </c>
       <c r="J21" t="n">
         <v>11.1</v>
@@ -14133,11 +14022,9 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="I22" t="n">
-        <v>53.4</v>
-      </c>
+        <v>29.7</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>7.8</v>
       </c>
@@ -14182,11 +14069,9 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="I23" t="n">
-        <v>11.5</v>
-      </c>
+        <v>29.5</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>1.7</v>
       </c>
@@ -14235,10 +14120,10 @@
         <v>-10.54</v>
       </c>
       <c r="H24" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.5</v>
+        <v>15.2</v>
       </c>
       <c r="J24" t="n">
         <v>9</v>
@@ -14292,10 +14177,10 @@
         <v>-12.08</v>
       </c>
       <c r="H25" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="I25" t="n">
-        <v>80.40000000000001</v>
+        <v>37.8</v>
       </c>
       <c r="J25" t="n">
         <v>29.1</v>
@@ -14308,7 +14193,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
+          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
         </is>
       </c>
     </row>
@@ -14345,7 +14230,7 @@
         <v>-9</v>
       </c>
       <c r="H26" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
@@ -14361,11 +14246,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
-        </is>
-      </c>
+      <c r="M26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -14400,11 +14281,9 @@
         <v>2.59</v>
       </c>
       <c r="H27" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I27" t="n">
-        <v>13.5</v>
-      </c>
+        <v>25.1</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>1</v>
       </c>
@@ -14453,11 +14332,9 @@
         <v>-17.2</v>
       </c>
       <c r="H28" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I28" t="n">
-        <v>355.9</v>
-      </c>
+        <v>22.6</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>50</v>
       </c>
@@ -14467,11 +14344,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
-        </is>
-      </c>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -14506,10 +14379,10 @@
         <v>-6.76</v>
       </c>
       <c r="H29" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="I29" t="n">
-        <v>178.9</v>
+        <v>26.3</v>
       </c>
       <c r="J29" t="n">
         <v>15.3</v>
@@ -14559,11 +14432,9 @@
         <v>1.45</v>
       </c>
       <c r="H30" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>16.6</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>1.8</v>
       </c>
@@ -14573,11 +14444,7 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
-        </is>
-      </c>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -14612,11 +14479,9 @@
         <v>-5.13</v>
       </c>
       <c r="H31" t="n">
-        <v>18</v>
-      </c>
-      <c r="I31" t="n">
-        <v>35.7</v>
-      </c>
+        <v>17.9</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>3.6</v>
       </c>
@@ -14665,11 +14530,9 @@
         <v>-7.88</v>
       </c>
       <c r="H32" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I32" t="n">
-        <v>55.8</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
         <v>10.3</v>
       </c>
@@ -14761,7 +14624,7 @@
         <v>-11.36</v>
       </c>
       <c r="H34" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
@@ -14775,7 +14638,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
+          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
         </is>
       </c>
     </row>
@@ -14812,11 +14675,9 @@
         <v>-8.539999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I35" t="n">
-        <v>52</v>
-      </c>
+        <v>14.8</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>17.5</v>
       </c>
@@ -14863,9 +14724,7 @@
       <c r="H36" t="n">
         <v>14.6</v>
       </c>
-      <c r="I36" t="n">
-        <v>29.6</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>2.5</v>
       </c>
@@ -14910,10 +14769,10 @@
         <v>-4.64</v>
       </c>
       <c r="H37" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>18.9</v>
+        <v>33.5</v>
       </c>
       <c r="J37" t="n">
         <v>6.6</v>
@@ -14959,9 +14818,11 @@
         <v>-10</v>
       </c>
       <c r="H38" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>23.3</v>
+      </c>
       <c r="J38" t="n">
         <v>3.9</v>
       </c>
@@ -15009,7 +14870,7 @@
         <v>12.5</v>
       </c>
       <c r="I39" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="J39" t="n">
         <v>1.8</v>
@@ -15057,9 +14918,7 @@
       <c r="H40" t="n">
         <v>12</v>
       </c>
-      <c r="I40" t="n">
-        <v>659.3</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>7.8</v>
       </c>
@@ -15107,7 +14966,7 @@
         <v>11.7</v>
       </c>
       <c r="I41" t="n">
-        <v>27.7</v>
+        <v>22.7</v>
       </c>
       <c r="J41" t="n">
         <v>3.1</v>
@@ -15159,9 +15018,7 @@
       <c r="H42" t="n">
         <v>11.5</v>
       </c>
-      <c r="I42" t="n">
-        <v>41</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>11.1</v>
       </c>
@@ -15173,7 +15030,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
+          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15125,7 @@
         <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>78.7</v>
+        <v>48.7</v>
       </c>
       <c r="J44" t="n">
         <v>3.1</v>
@@ -15314,11 +15171,9 @@
         <v>-2.96</v>
       </c>
       <c r="H45" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I45" t="n">
-        <v>36.2</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
         <v>3.5</v>
       </c>
@@ -15369,9 +15224,7 @@
       <c r="H46" t="n">
         <v>10.6</v>
       </c>
-      <c r="I46" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>1</v>
       </c>
@@ -15416,9 +15269,11 @@
         <v>-12.56</v>
       </c>
       <c r="H47" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>235.5</v>
+      </c>
       <c r="J47" t="n">
         <v>36.9</v>
       </c>
@@ -15428,11 +15283,7 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="11" t="inlineStr">
-        <is>
-          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
-        </is>
-      </c>
+      <c r="M47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -15469,9 +15320,7 @@
       <c r="H48" t="n">
         <v>10.1</v>
       </c>
-      <c r="I48" t="n">
-        <v>35.5</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>13.5</v>
       </c>

--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -6740,7 +6740,11 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="11" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -6938,7 +6942,11 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -7093,7 +7101,11 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7344,7 +7356,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -7442,7 +7458,11 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -7597,7 +7617,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -7650,7 +7674,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -8058,7 +8086,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -8260,7 +8292,11 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="11" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -8415,7 +8451,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -8666,7 +8706,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8825,7 +8869,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -9135,7 +9183,7 @@
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
+          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9238,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -9997,7 +10049,11 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -10246,7 +10302,11 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -10507,7 +10567,11 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="11" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -10864,7 +10928,11 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -11223,7 +11291,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -11272,7 +11344,11 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="11" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -11321,7 +11397,11 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>마키타(전동공구): 1분기 이익 상회분 대부분 관세환급 일회성·실수요 부진·서유럽 -11%에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -11571,7 +11651,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -11720,7 +11804,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
+          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
         </is>
       </c>
     </row>
@@ -11934,7 +12018,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -12087,7 +12175,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -12138,7 +12230,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
+          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12558,11 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -12519,7 +12615,7 @@
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
+          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12937,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -12890,7 +12990,11 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M28"/>
@@ -13242,7 +13346,11 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -13444,7 +13552,11 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -13493,7 +13605,11 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -13589,7 +13705,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -13689,7 +13809,11 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -13889,7 +14013,11 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -14193,7 +14321,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
+          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14374,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -14344,7 +14476,11 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -14444,7 +14580,11 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -14638,7 +14778,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
+          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15170,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
+          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
         </is>
       </c>
     </row>
@@ -15283,7 +15423,11 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">

--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -619,35 +619,35 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 미 실적시즌 메가캡 테크·헬스케어 서프라이즈로 3대지수 동반 강세, 반면 중화권은 광모듈·반도체 급락 vs 은행 고배당 순환매로 양극화 국면.</t>
+          <t>💬 ■ 결론: 오늘 새벽 마감한 미장은 실적 서프라이즈발 불반등(나스닥 +2.78%), 반면 직전 마감 중화권은 AI하드웨어 급락 vs 은행 순환매로 정반대 국면 — 같은 날 안에서 지역 디커플링.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ 美: 나스닥 +2.78%·S&amp;P +1.66%·다우 +1.19%. 강세는 금융(순강도+10)·헬스(+6, CORT +27%·REGN·ILMN 실적호조), XLK 테크ETF +5.5%로 메가캡 주도. 약세는 Producer Manufacturing(순강도-7)·담배 알트리아 -9%·방산 L3해리스 -8.6%·물류 CH로빈슨 -15% 실적 실망.</t>
+          <t>■ 美(한국시간 7/31 새벽 마감, 현지 7/30장): 나스닥 +2.78%·S&amp;P +1.66%·다우 +1.19%. 강세 금융(순강도+10, 12MF PER 15.3)·헬스(+6, 20.0배)로 CORT +27%·REGN·ILMN 실적 호조, XLK +5.5%. 약세는 Producer Manufacturing(-7, 23.9배)·CH로빈슨 -15%(배상판결)·알트리아 -9%·L3해리스 -8.6%. 메타는 AI지출로 잉여현금 -91%에 -8%.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 日: 은행ETF -3.4%·자동차 -2.2% 약세 우위, 전기정밀 +2.5%(NEC 1분기 순익 2.6배로 +8%). 마키타 관세환급 일회성에 -10%, 주부전력 적자전환·키오시아 메모리 우려로 신저가.</t>
+          <t>■ 日(7/30 마감): 은행ETF -3.4%·자동차 -2.2% 약세 우위, 전기정밀 +2.5%. NEC 1분기 순익 2.6배로 +8%, 마키타 관세환급 일회성에 -10%, 키오시아 메모리 피크아웃 우려 신저가.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ 中·홍콩: 상해 -0.62%·CSI300 -1.10%·항셍테크 -1.25%. 공통 축은 은행(순강도 中+9/홍+7) 고배당 순환매로 신고가 vs AI 하드웨어 급락(中 전자기술 순강도 -16). 中지쉬촹 홍콩 IPO 첫날 붕괴에 광모듈(신이성·톈푸퉁신 등) 동반 급락, 홍콩 중신궈지 -7.7%.</t>
+          <t>■ 中·홍콩(7/30 마감): 상해 -0.62%·CSI300 -1.10%·항셍테크 -1.25%. 은행(中 순강도+9 PER 6.3배, 홍 +7 11.4배) 고배당 순환매 신고가 vs 전자기술(中 -16 30.3배, 홍 -6) 급락. 중지쉬촹 홍콩 IPO 첫날 붕괴가 광모듈 연쇄 급락 촉발, 중신궈지 -7.7%.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①남은 미 메가캡 실적·AI capex 코멘트 ②중화권 광모듈·반도체 조정 지속 여부 ③은행 방어 순환매 지속성.</t>
+          <t>■ 체크: ①미 불반등이 중화권 AI하드웨어로 전이될지(오늘 아시아장 관전) ②광모듈 밸류 조정 지속 여부 ③은행 방어 순환매 지속성.</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$I$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$M$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$M$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$M$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$M$48</definedName>
   </definedNames>
@@ -77,14 +77,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -550,7 +549,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -559,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -899,14 +898,32 @@
           <t>상해종합</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>3804.69</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -919,14 +936,32 @@
           <t>CSI300</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>4549.72</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="I7" t="n">
+        <v>49</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -939,14 +974,32 @@
           <t>항셍</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>25858.88</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -959,14 +1012,32 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>4803.77</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-12.91</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1063,7 +1134,7 @@
       <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1098,7 +1169,7 @@
       <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1133,7 +1204,7 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1168,7 +1239,7 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1203,7 +1274,7 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1238,7 +1309,7 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1273,7 +1344,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1308,7 +1379,7 @@
       <c r="F9" t="n">
         <v>-1</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1343,7 +1414,7 @@
       <c r="F10" t="n">
         <v>-2</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1378,7 +1449,7 @@
       <c r="F11" t="n">
         <v>-2</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1413,13 +1484,13 @@
       <c r="F12" t="n">
         <v>-2</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="I12" t="n">
         <v>2.9</v>
@@ -1448,7 +1519,7 @@
       <c r="F13" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1483,7 +1554,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1518,7 +1589,7 @@
       <c r="F15" t="n">
         <v>-7</v>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1763,7 +1834,7 @@
       <c r="F22" t="n">
         <v>6</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1787,24 +1858,24 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="I23" t="n">
         <v>1.4</v>
@@ -1833,7 +1904,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1868,7 +1939,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1903,7 +1974,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1938,7 +2009,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1973,7 +2044,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2008,7 +2079,7 @@
       <c r="F29" t="n">
         <v>-1</v>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2028,7 +2099,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2043,16 +2114,16 @@
       <c r="F30" t="n">
         <v>-1</v>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2063,11 +2134,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -2078,16 +2149,16 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="32">
@@ -2098,11 +2169,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -2113,16 +2184,16 @@
       <c r="F32" t="n">
         <v>-1</v>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>15.4</v>
+        <v>12.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33">
@@ -2133,31 +2204,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>12.7</v>
+        <v>24.4</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="34">
@@ -2168,31 +2239,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>혼조</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>24.4</v>
+        <v>17.9</v>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="35">
@@ -2203,28 +2274,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>혼조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="I35" t="n">
         <v>1.9</v>
@@ -2238,11 +2309,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -2259,10 +2330,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>14.3</v>
+        <v>9.6</v>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="37">
@@ -2273,11 +2344,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2294,10 +2365,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9.6</v>
+        <v>14.3</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="38">
@@ -2308,11 +2379,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2329,10 +2400,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>14.3</v>
+        <v>20.3</v>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="39">
@@ -2343,11 +2414,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2364,10 +2435,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>20.3</v>
+        <v>13.2</v>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2393,7 +2464,7 @@
       <c r="F40" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2428,7 +2499,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2463,7 +2534,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2498,7 +2569,7 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2533,7 +2604,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2568,7 +2639,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2603,7 +2674,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2638,7 +2709,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2673,7 +2744,7 @@
       <c r="F48" t="n">
         <v>-3</v>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2708,7 +2779,7 @@
       <c r="F49" t="n">
         <v>-6</v>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3023,7 +3094,7 @@
       <c r="F58" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3058,7 +3129,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3093,7 +3164,7 @@
       <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3128,7 +3199,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3163,7 +3234,7 @@
       <c r="F62" t="n">
         <v>-1</v>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3196,7 +3267,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3231,7 +3302,7 @@
       <c r="F64" t="n">
         <v>-2</v>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3266,7 +3337,7 @@
       <c r="F65" t="n">
         <v>-2</v>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3290,7 +3361,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -3301,7 +3372,7 @@
       <c r="F66" t="n">
         <v>-7</v>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3310,7 +3381,7 @@
         <v>29.2</v>
       </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="67">
@@ -3336,7 +3407,7 @@
       <c r="F67" t="n">
         <v>-16</v>
       </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3792,60 +3863,60 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>메가캡 테크 실적 서프라이즈로 당일 +5.5% 급등, 다만 전자기술 순강도 -2로 breadth는 대형주 편중</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="9" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="O2" s="10" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="10" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
       <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="S2" s="10" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
       <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="U2" s="10" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
       <c r="V2" t="n">
@@ -3868,60 +3939,60 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>CORT +27%·REGN·ILMN 개별 실적주 강세, 다만 ALNY -28% 미스 혼재로 ETF -1.6%</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I3" s="9" t="n">
         <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" s="10" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
       <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="10" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
       <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="Q3" s="10" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
       <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="S3" s="10" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
       <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="U3" s="10" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
       <c r="V3" t="n">
@@ -3944,60 +4015,60 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>신고-신저 순강도 +10 전 섹터 최강, 은행·보험 신고가 다수로 가치·방어 선호(+0.6%)</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
       <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
       <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="S4" s="10" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="U4" s="10" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
       <c r="V4" t="n">
@@ -4020,60 +4091,60 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>치폴레 +12.5% 등 외식·서비스 실적 개선에 당일 +0.7%</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="9" t="n">
         <v>-5.5</v>
       </c>
       <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="S5" s="10" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
       <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
       <c r="V5" t="n">
@@ -4096,60 +4167,60 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>당일 -2.7%로 전 섹터 최약, 광고·미디어 대형주 실적 경계</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="9" t="n">
         <v>-7.3</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="9" t="n">
         <v>-8.9</v>
       </c>
       <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
       <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
       <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="U6" s="10" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
       <c r="V6" t="n">
@@ -4172,60 +4243,60 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>ETF +1.0%에도 Producer Manufacturing 순강도 -7로 breadth 약세, 방산 L3해리스 -8.6% 신저가</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="9" t="n">
         <v>15.6</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="S7" s="10" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
       <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U7" s="10" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="V7" t="n">
@@ -4248,60 +4319,60 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>담배 알트리아 -9.3% 실적 실망 등으로 당일 -2.2% 약세</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
       <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
       <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
       <c r="V8" t="n">
@@ -4324,60 +4395,60 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>1개월 +11%로 상대강세 지속, 당일 +0.5%</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="9" t="n">
         <v>33.7</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
       <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
       <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" s="10" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="10" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
       <c r="V9" t="n">
@@ -4400,60 +4471,60 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>당일 -0.6% 소폭 약세, 뚜렷한 촉매 없음</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="9" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>8</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
       <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S10" s="10" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="V10" t="n">
@@ -4476,60 +4547,60 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>당일 -0.2% 보합권, 방향성 부재</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I11" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
       <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="S11" s="10" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
       <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="U11" s="10" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="V11" t="n">
@@ -4552,60 +4623,60 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>ETF -1.4% 약세이나 JLL +6.4% 실적 서프라이즈로 52주 신고가 개별 차별화</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="9" t="n">
         <v>14</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
       <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
       <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="S12" s="10" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="U12" s="10" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
       <c r="V12" t="n">
@@ -4628,56 +4699,56 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="10" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
       <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
       <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="S13" s="10" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
       <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="U13" s="10" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
       <c r="V13" t="n">
@@ -4700,56 +4771,56 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="10" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H14" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I14" s="9" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
       <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
       <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
       <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="S14" s="10" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="10" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
       <c r="V14" t="n">
@@ -4772,56 +4843,56 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="10" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="9" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="O15" s="10" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
       <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
       <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="S15" s="10" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
       <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="U15" s="10" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
       <c r="V15" t="n">
@@ -4844,56 +4915,56 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="10" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
       <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="O16" s="10" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
       <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="S16" s="10" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
       <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="U16" s="10" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="V16" t="n">
@@ -4916,56 +4987,56 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="10" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I17" s="9" t="n">
         <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="K17" s="10" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="O17" s="10" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="S17" s="10" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
       <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="U17" s="10" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
       <c r="V17" t="n">
@@ -4988,56 +5059,56 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="10" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="O18" s="10" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
       <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
       <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="U18" s="10" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
       <c r="V18" t="n">
@@ -5060,56 +5131,56 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="10" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="9" t="n">
         <v>-11.8</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="9" t="n">
         <v>-22.3</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" s="9" t="n">
         <v>-21.8</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I19" s="9" t="n">
         <v>25.9</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="10" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="O19" s="10" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
       <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
       <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="S19" s="10" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="U19" s="10" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
       <c r="V19" t="n">
@@ -5132,56 +5203,56 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr"/>
-      <c r="E20" s="10" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="9" t="n">
         <v>-6.3</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H20" s="9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I20" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="K20" s="10" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
       <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="O20" s="10" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
       <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
       <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="S20" s="10" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
       <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="U20" s="10" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="V20" t="n">
@@ -5204,56 +5275,56 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr"/>
-      <c r="E21" s="10" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="n">
         <v>-6.7</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="9" t="n">
         <v>-14.3</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="I21" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
       <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="O21" s="10" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
       <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
       <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="S21" s="10" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
       <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="U21" s="10" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
       <c r="V21" t="n">
@@ -5276,56 +5347,56 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="10" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I22" s="9" t="n">
         <v>6.9</v>
       </c>
       <c r="J22" t="n">
         <v>12</v>
       </c>
-      <c r="K22" s="10" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
       <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="O22" s="10" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
       <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
       <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="U22" s="10" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
       <c r="V22" t="n">
@@ -5348,56 +5419,56 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="10" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="K23" s="10" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
       <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="O23" s="10" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
       <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="S23" s="10" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="U23" s="10" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
       <c r="V23" t="n">
@@ -5420,56 +5491,56 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="10" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" s="9" t="n">
         <v>7.2</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
       </c>
-      <c r="K24" s="10" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="O24" s="10" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
       <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="S24" s="10" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
       <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="U24" s="10" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
       <c r="V24" t="n">
@@ -5492,56 +5563,56 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="10" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="9" t="n">
         <v>16</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
-      <c r="K25" s="10" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
       <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
       <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="O25" s="10" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="S25" s="10" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
       <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U25" s="10" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="V25" t="n">
@@ -5564,56 +5635,56 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="10" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I26" s="9" t="n">
         <v>7.4</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" s="10" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="O26" s="10" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="S26" s="10" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
       <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="U26" s="10" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="V26" t="n">
@@ -5636,56 +5707,56 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="10" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="9" t="n">
         <v>40.7</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="10" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
       <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
       <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="U27" s="10" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
       <c r="V27" t="n">
@@ -5708,56 +5779,56 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="10" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" s="9" t="n">
         <v>31.6</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="10" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="O28" s="10" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
       <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="S28" s="10" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="U28" s="10" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
       <c r="V28" t="n">
@@ -5780,56 +5851,56 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="10" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H29" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I29" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="K29" s="10" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="O29" s="10" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
       <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="S29" s="10" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
       <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="U29" s="10" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
       <c r="V29" t="n">
@@ -5852,25 +5923,61 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr"/>
-      <c r="G30" s="10" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" s="10" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" s="10" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" s="10" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" s="10" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" s="10" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5888,25 +5995,61 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" s="10" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" s="10" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" s="10" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5924,24 +6067,56 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" s="10" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" s="10" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" s="10" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" s="10" t="inlineStr"/>
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" s="9" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5960,29 +6135,65 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 전자기술 순강도 -16 최약, 광모듈·반도체 신저가 속출로 약세 추정</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" s="10" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" s="10" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" s="10" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" s="10" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="E33" s="9" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>-34.9</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>12</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6000,29 +6211,65 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 기술주 전반 약세, 광모듈·반도체 조정에 약세 추정</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr"/>
-      <c r="F34" s="10" t="inlineStr"/>
-      <c r="G34" s="10" t="inlineStr"/>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="10" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" s="10" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" s="10" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" s="10" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" s="10" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="E34" s="9" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="R34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6040,29 +6287,65 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 광통신·부품 약세 연동 추정(통신 순강도 중립)</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr"/>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" s="10" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" s="10" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" s="10" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" s="10" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="E35" s="9" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>13</v>
+      </c>
+      <c r="S35" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6080,28 +6363,60 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 소비내구재 순강도 +2 강세, 신에너지차 상대 견조 추정</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="10" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr"/>
-      <c r="I36" s="10" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" s="10" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" s="10" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" s="10" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" s="10" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" s="10" t="inlineStr"/>
+      <c r="E36" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>-29</v>
+      </c>
+      <c r="P36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="R36" t="n">
+        <v>10</v>
+      </c>
+      <c r="S36" s="9" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" s="9" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -6120,29 +6435,65 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 제조업 breadth 약세, 방산 뚜렷한 촉매 없음 추정</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="10" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr"/>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" s="10" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" s="10" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" s="10" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="E37" s="9" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>13</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>8</v>
+      </c>
+      <c r="S37" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6160,28 +6511,60 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 신재생·제조 breadth 약세 추정</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr"/>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="10" t="inlineStr"/>
-      <c r="H38" s="10" t="inlineStr"/>
-      <c r="I38" s="10" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" s="10" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" s="10" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" s="10" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" s="10" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" s="10" t="inlineStr"/>
+      <c r="E38" s="9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>11</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="R38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S38" s="9" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="9" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6200,29 +6583,65 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 소비 중립, 방향성 부재 추정</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="10" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" s="10" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" s="10" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" s="10" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" s="10" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="E39" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L39" t="n">
+        <v>13</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N39" t="n">
+        <v>11</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>9</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6240,29 +6659,65 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 금융 순강도 +9 최강, 은행 고배당 순환매로 신고가 다수 강세 추정</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr"/>
-      <c r="F40" s="10" t="inlineStr"/>
-      <c r="G40" s="10" t="inlineStr"/>
-      <c r="H40" s="10" t="inlineStr"/>
-      <c r="I40" s="10" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" s="10" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" s="10" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" s="10" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" s="10" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" s="10" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="E40" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" s="9" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>7</v>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V40" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6280,29 +6735,65 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 비철금속 순강도 -2 약세 추정</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr"/>
-      <c r="I41" s="10" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" s="10" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" s="10" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" s="10" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="E41" s="9" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q41" s="9" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6</v>
+      </c>
+      <c r="S41" s="9" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="V41" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6320,29 +6811,65 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 부동산 뚜렷한 촉매 없음 추정</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr"/>
-      <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="10" t="inlineStr"/>
-      <c r="H42" s="10" t="inlineStr"/>
-      <c r="I42" s="10" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" s="10" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" s="10" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" s="10" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" s="10" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" s="10" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="E42" s="9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>12</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>9</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>-27</v>
+      </c>
+      <c r="P42" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" s="9" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>11</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6360,29 +6887,65 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 금융 강세 흐름 일부 수혜 추정, 증권 개별 촉매 미확인</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="10" t="inlineStr"/>
-      <c r="G43" s="10" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr"/>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" s="10" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" s="10" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" s="10" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" s="10" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>8</v>
+      </c>
+      <c r="S43" s="9" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="T43" t="n">
+        <v>10</v>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6400,29 +6963,65 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 의약 중립, 방향성 부재 추정</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr"/>
-      <c r="F44" s="10" t="inlineStr"/>
-      <c r="G44" s="10" t="inlineStr"/>
-      <c r="H44" s="10" t="inlineStr"/>
-      <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" s="10" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" s="10" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" s="10" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" s="10" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" s="10" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="E44" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>12</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>-14</v>
+      </c>
+      <c r="P44" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7</v>
+      </c>
+      <c r="S44" s="9" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>13</v>
+      </c>
+      <c r="U44" s="9" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V44" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6440,29 +7039,65 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>당일 ETF 시세 수집 실패(공란). 소비 중립, 방어주 선호 일부 추정</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="10" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" s="10" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" s="10" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="E45" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="P45" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" s="9" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>12</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6475,7 +7110,7 @@
   <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-3.4"/>
+        <cfvo type="num" val="-7.8"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="5.5"/>
         <color rgb="007A9BFF"/>
@@ -6487,9 +7122,9 @@
   <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-11.8"/>
+        <cfvo type="num" val="-16.7"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5.6"/>
+        <cfvo type="num" val="6.4"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6499,9 +7134,9 @@
   <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="num" val="-22.3"/>
+        <cfvo type="num" val="-34.9"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="13.3"/>
+        <cfvo type="num" val="16.3"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6511,7 +7146,7 @@
   <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-21.8"/>
+        <cfvo type="num" val="-22.7"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="22.9"/>
         <color rgb="007A9BFF"/>
@@ -6523,7 +7158,7 @@
   <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="num" val="-8.9"/>
+        <cfvo type="num" val="-21.8"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="40.7"/>
         <color rgb="007A9BFF"/>
@@ -6535,8 +7170,10 @@
   <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
+        <cfvo type="num" val="-13"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="68.8"/>
+        <cfvo type="num" val="101.1"/>
+        <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
       </colorScale>
@@ -6545,8 +7182,10 @@
   <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
+        <cfvo type="num" val="-14.9"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50.4"/>
+        <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
       </colorScale>
@@ -6555,7 +7194,7 @@
   <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
-        <cfvo type="num" val="-7.2"/>
+        <cfvo type="num" val="-35.2"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="56"/>
         <color rgb="007A9BFF"/>
@@ -6567,7 +7206,7 @@
   <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
-        <cfvo type="num" val="-37.6"/>
+        <cfvo type="num" val="-37.8"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="64.3"/>
         <color rgb="007A9BFF"/>
@@ -6579,7 +7218,7 @@
   <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="num" val="-8.4"/>
+        <cfvo type="num" val="-32.9"/>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="53.3"/>
         <color rgb="007A9BFF"/>
@@ -6593,7 +7232,7 @@
       <colorScale>
         <cfvo type="num" val="-32.7"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="43.6"/>
+        <cfvo type="num" val="336.4"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6696,7 +7335,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6740,14 +7379,10 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="11" t="inlineStr">
-        <is>
-          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
-        </is>
-      </c>
+      <c r="M2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -6793,10 +7428,10 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6842,10 +7477,10 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -6895,10 +7530,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6942,14 +7577,10 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
-        </is>
-      </c>
+      <c r="M6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -6999,14 +7630,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>(전일) 스노우플레이크(클라우드 데이터플랫폼): 웰스파고 목표가 $320→$500 상향·AI에이전트 지출 가속 논거</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7052,10 +7683,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7101,14 +7732,10 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
-        </is>
-      </c>
+      <c r="M9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7154,10 +7781,10 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7203,10 +7830,10 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7252,10 +7879,10 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="11" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7305,10 +7932,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7356,14 +7983,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
-        </is>
-      </c>
+      <c r="M14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7409,10 +8032,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7458,14 +8081,10 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7515,10 +8134,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7564,10 +8183,10 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="11" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7617,14 +8236,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7674,14 +8289,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
-        </is>
-      </c>
+      <c r="M20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7727,10 +8338,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7776,14 +8387,14 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전서비스): 실적 상회에도 에너지 섹터 약세·유가 불확실성으로 하락</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7833,10 +8444,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7886,10 +8497,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7935,10 +8546,10 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7984,10 +8595,10 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="11" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8033,10 +8644,10 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="11" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8086,14 +8697,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
-        </is>
-      </c>
+      <c r="M28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8143,10 +8750,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8196,10 +8803,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8245,10 +8852,10 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="11" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8292,14 +8899,10 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
-        </is>
-      </c>
+      <c r="M32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8349,10 +8952,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8398,10 +9001,10 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="11" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8451,14 +9054,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
-        </is>
-      </c>
+      <c r="M35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8504,10 +9103,10 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="11" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8557,10 +9156,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="11" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8606,10 +9205,10 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="11" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8653,10 +9252,10 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="11" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8706,14 +9305,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr">
-        <is>
-          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
-        </is>
-      </c>
+      <c r="M40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8763,14 +9358,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="11" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>(전일) 레녹스인터내셔널(주거용 HVAC): 2Q매출 소폭 미달·FY EPS가이던스 $23.50으로 하향(컨센 -4.7%)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8816,10 +9411,10 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="11" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8869,14 +9464,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr">
-        <is>
-          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8922,10 +9513,10 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="11" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8975,14 +9566,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>(전일) (캐주얼다이닝): 다수 증권사 목표가 상향(웰스파고 $220)·소고기값 완화 기대</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9028,14 +9619,14 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="11" t="inlineStr">
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>(전일) (산업용 바코드·모바일컴퓨터): 소프트웨어·AI분석 수요 회복 기대, 목표가 연속 상향으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9081,10 +9672,10 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="11" t="inlineStr"/>
+      <c r="M47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9130,10 +9721,10 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="11" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9181,14 +9772,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M49" s="11" t="inlineStr">
-        <is>
-          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9238,14 +9829,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
-        </is>
-      </c>
+      <c r="M50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9293,14 +9880,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M51" s="11" t="inlineStr">
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓스코(HVAC유통): 2Q EPS $4.00 컨센 $4.39 미달·매출총이익률 27.5%로 전년比 축소</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9344,10 +9931,10 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="11" t="inlineStr"/>
+      <c r="M52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9391,14 +9978,14 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>(전일) 에버코어(독립자문 투자은행): 2Q EPS 소폭 상회했으나 1Q 역대최고 대비 실망·'뉴스에 팔자'</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9444,10 +10031,10 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="11" t="inlineStr"/>
+      <c r="M54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9497,10 +10084,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M55" s="11" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9550,10 +10137,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M56" s="11" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9603,10 +10190,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M57" s="11" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9652,10 +10239,10 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="11" t="inlineStr"/>
+      <c r="M58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9699,10 +10286,10 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="11" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9752,10 +10339,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M60" s="11" t="inlineStr"/>
+      <c r="M60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9805,7 +10392,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M61" s="11" t="inlineStr"/>
+      <c r="M61" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M61"/>
@@ -9819,7 +10406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9905,7 +10492,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9937,7 +10524,7 @@
         <v>-2.51</v>
       </c>
       <c r="H2" t="n">
-        <v>169.6</v>
+        <v>168.8</v>
       </c>
       <c r="I2" t="n">
         <v>42.5</v>
@@ -9951,10 +10538,10 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="11" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9986,7 +10573,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>141.4</v>
+        <v>140.7</v>
       </c>
       <c r="I3" t="n">
         <v>18.6</v>
@@ -10000,10 +10587,10 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10035,7 +10622,7 @@
         <v>2.92</v>
       </c>
       <c r="H4" t="n">
-        <v>131.8</v>
+        <v>131.2</v>
       </c>
       <c r="I4" t="n">
         <v>3.9</v>
@@ -10049,14 +10636,10 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
-        </is>
-      </c>
+      <c r="M4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10088,7 +10671,7 @@
         <v>-1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>111.4</v>
+        <v>110.9</v>
       </c>
       <c r="I5" t="n">
         <v>29.7</v>
@@ -10106,10 +10689,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10141,7 +10724,7 @@
         <v>-1.83</v>
       </c>
       <c r="H6" t="n">
-        <v>70.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="I6" t="n">
         <v>16.1</v>
@@ -10159,10 +10742,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10194,7 +10777,7 @@
         <v>1.99</v>
       </c>
       <c r="H7" t="n">
-        <v>57.7</v>
+        <v>57.4</v>
       </c>
       <c r="I7" t="n">
         <v>25.1</v>
@@ -10208,10 +10791,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10243,7 +10826,7 @@
         <v>1.51</v>
       </c>
       <c r="H8" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
@@ -10255,10 +10838,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10290,7 +10873,7 @@
         <v>8.43</v>
       </c>
       <c r="H9" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
@@ -10302,14 +10885,10 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
-        </is>
-      </c>
+      <c r="M9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10341,7 +10920,7 @@
         <v>-0.48</v>
       </c>
       <c r="H10" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="I10" t="n">
         <v>14.2</v>
@@ -10355,14 +10934,14 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>(전일) (자동차부품 1위): 7/31 결산 앞둔 기대매수, 日증시 반등 수혜</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10394,7 +10973,7 @@
         <v>1.07</v>
       </c>
       <c r="H11" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="I11" t="n">
         <v>28.1</v>
@@ -10408,14 +10987,14 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>(전일) (디스코·반도체 다이싱장비): 7-9월 순이익 가이던스 395억엔이 컨센 473억엔 대폭 하회로 -12% 급락</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10447,7 +11026,7 @@
         <v>-1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
@@ -10463,14 +11042,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>(전일) (브리지스톤·타이어): 1Q 경상이익 +47% 호조, 8/7 결산 기대 매수로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10502,7 +11081,7 @@
         <v>-3.63</v>
       </c>
       <c r="H13" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
@@ -10514,14 +11093,14 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>(전일) (도쿄디즈니리조트): 입장권 상한 인상 보도·7/30 결산 기대로 연속 급등</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10553,7 +11132,7 @@
         <v>0.27</v>
       </c>
       <c r="H14" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="I14" t="n">
         <v>19.2</v>
@@ -10567,14 +11146,10 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
-        </is>
-      </c>
+      <c r="M14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10606,7 +11181,7 @@
         <v>-2.07</v>
       </c>
       <c r="H15" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I15" t="n">
         <v>30.6</v>
@@ -10620,14 +11195,14 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>(전일) 레이저테크(EUV 마스크검사장비): SK하이닉스 실적 미달+한국증시 서킷브레이커로 장비주 집중매도</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10659,7 +11234,7 @@
         <v>-3.81</v>
       </c>
       <c r="H16" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="I16" t="n">
         <v>21.5</v>
@@ -10673,14 +11248,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>(전일) 코나미그룹(게임·헬스클럽 복합): 카프콤 1Q 영업익 +67% 호실적에 게임주 전반 동반매수</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10712,7 +11287,7 @@
         <v>-0.17</v>
       </c>
       <c r="H17" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
         <v>21.6</v>
@@ -10726,14 +11301,14 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>(전일) (게임·완구): 맥쿼리 목표주가 5500→5600엔 상향, 8/5 결산 기대매수</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10765,7 +11340,7 @@
         <v>1.51</v>
       </c>
       <c r="H18" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
@@ -10777,14 +11352,14 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>(전일) (IT컨설팅·NRI): 7/30 결산 앞두고 기대 매수, FY27 이익 전망 개선으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10816,7 +11391,7 @@
         <v>-0.65</v>
       </c>
       <c r="H19" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="I19" t="n">
         <v>11.2</v>
@@ -10830,10 +11405,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10865,7 +11440,7 @@
         <v>-0.98</v>
       </c>
       <c r="H20" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
@@ -10877,14 +11452,14 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>(전일) (레조낙·반도체소재): 중국 노광장비 자체제조 보도·아시아 AI반도체 전반 급락 수급으로 신저가</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10928,14 +11503,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
-        </is>
-      </c>
+      <c r="M21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10947,84 +11518,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>4684 JP Equity</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OBIC Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Technology Services</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4736</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (ERP·업무SW): 4-6월 순이익 16%↑ 결산 재평가, IT섹터로 자금 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>7270 JP Equity</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Subaru Corporation</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>2823</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-0.9</v>
-      </c>
-      <c r="H22" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I22" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>(전일) 스바루(자동차): AI반도체 섹터 급락에 저배당·저PBR 자동차주로 자금이동</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4684 JP Equity</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OBIC Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Technology Services</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>4736</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.34</v>
       </c>
       <c r="H23" t="n">
         <v>12.7</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>9.9</v>
+      </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -11032,14 +11603,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>(전일) (ERP·업무SW): 4-6월 순이익 16%↑ 결산 재평가, IT섹터로 자금 이동</t>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 스바루(자동차): AI반도체 섹터 급락에 저배당·저PBR 자동차주로 자금이동</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11071,7 +11642,7 @@
         <v>-0.32</v>
       </c>
       <c r="H24" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
@@ -11083,10 +11654,10 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="11" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11098,101 +11669,101 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>7259 JP Equity</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aisin Corporation</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Producer Manufacturing</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2518.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>7309 JP Equity</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Shimano Inc.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>20970</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>(전일) 시마노(자전거 부품·낚시): 2Q 순익 +606% 급증 호실적에 상반기 업적 상방수정</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>7259 JP Equity</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Aisin Corporation</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Producer Manufacturing</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>2518.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.24</v>
       </c>
       <c r="H26" t="n">
         <v>11.3</v>
       </c>
       <c r="I26" t="n">
-        <v>11.7</v>
+        <v>34.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" s="11" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 시마노(자전거 부품·낚시): 2Q 순익 +606% 급증 호실적에 상반기 업적 상방수정</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11224,7 +11795,7 @@
         <v>0.78</v>
       </c>
       <c r="H27" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="I27" t="n">
         <v>25.3</v>
@@ -11238,10 +11809,10 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="11" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11273,7 +11844,7 @@
         <v>-1.63</v>
       </c>
       <c r="H28" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="I28" t="n">
         <v>25.6</v>
@@ -11291,14 +11862,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
-        </is>
-      </c>
+      <c r="M28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11344,114 +11911,10 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>6586 JP Equity</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Makita Corporation</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>5297</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-10.14</v>
-      </c>
-      <c r="H30" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>마키타(전동공구): 1분기 이익 상회분 대부분 관세환급 일회성·실수요 부진·서유럽 -11%에 급락</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1803 JP Equity</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Shimizu Corporation</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Industrial Services</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>2317.5</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="H31" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" s="11" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
+  <autoFilter ref="A1:M29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11548,7 +12011,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11596,14 +12059,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 독립 촉매 없이 은행 섹터 전반 강세·위안화 강세 수급으로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11651,14 +12114,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
-        </is>
-      </c>
+      <c r="M3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11706,10 +12165,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11753,10 +12212,10 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11802,14 +12261,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11857,14 +12316,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>(전일) (가전·로봇): 자사주 매입 집행·휴머노이드 상업화 기대 매수세 유입으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11910,14 +12369,14 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>(전일) (음식배달·로컬커머스): 미이란 긴장 완화 리스크오프 해소·과기주 매수, 2Q 적자축소 기대</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11963,14 +12422,14 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>(전일) (손해보험·중국재보험): 배당지급일 직전 막차 매수 집중, 은행·보험 방어섹터 동반 강세로 신고가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12018,14 +12477,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
-        </is>
-      </c>
+      <c r="M10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12069,14 +12524,14 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>(전일) 하이얼스마트홈(가전 제조): 신소비·대형소비주 섹터 수급 유입 동반 강세(개별 촉매 미확인, 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12126,10 +12581,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12175,14 +12630,10 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
-        </is>
-      </c>
+      <c r="M13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12228,14 +12679,14 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12285,14 +12736,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>(전일) 성훙테크H(AI서버 PCB): AI하드웨어 PCB 섹터 조정 지속·엔비디아 루빈 품질 루머 및 이익 정점 우려</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12338,14 +12789,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>(전일) 은하오락(마카오 카지노): 마카오 GGR 회복 기대·7월 일평균 매출 전주比 +9%·골드만 매수 유지</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12393,14 +12844,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>(전일) 딩타이가오커(PCB 드릴비트 글로벌 1위): AI서버 PCB 섹터 전반 급락(광허테크 등 -16%)에 동반</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12450,14 +12901,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>(전일) (복합기업·부동산): UBS 목표가 20% 상향, 태고지산·캐세이퍼시픽 이익 기여 기대로 신고가</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12507,14 +12958,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>(전일) 스와이어퍼시픽B(항공·부동산·음료 복합): 특별한 뉴스 없음(시장 전반 상승 흐름 동반 추정)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12558,14 +13009,10 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
-        </is>
-      </c>
+      <c r="M20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12613,14 +13060,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12666,14 +13113,14 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>(전일) 텐센트뮤직(온라인음악 스트리밍): 항셍테크 +2.84%, 텐센트·비리비리 등 대형 인터넷주 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12719,14 +13166,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>(전일) (동박적층판 PCB소재·젠타오): 엔비디아 차세대 AI서버랙 PCB 양산 2028년 연기 충격으로 -16% 급락</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12772,14 +13219,14 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>(전일) (국제택배·물류): 자사주 매입 지속, 동남아 패키지 처리량 +84% 역대 최대로 신고가</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12825,14 +13272,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>(전일) HKT트러스트(홍콩 통신): 7/30 중간 실적발표 앞두고 기대 매수 유입(+0.08% 소폭)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12882,14 +13329,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>(전일) (홍콩 국적 항공사): 캐세이퍼시픽, 상반기 순이익 60~65억 홍콩달러(전년비 최대 +76%) 예고, 여객·화물 호조</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12937,14 +13384,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
-        </is>
-      </c>
+      <c r="M27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12990,11 +13433,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="M28" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M28"/>
@@ -13094,7 +13533,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13126,7 +13565,7 @@
         <v>2.52</v>
       </c>
       <c r="H2" t="n">
-        <v>399.7</v>
+        <v>401.2</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
@@ -13138,14 +13577,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 창업판 급락 속 방어주 순환매로 은행섹터 강세, 공상은행 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13177,7 +13616,7 @@
         <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>351.9</v>
+        <v>353.2</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
@@ -13189,14 +13628,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>(전일) 농업은행(국유 대형은행): 섹터 선두 강세 후 신고가권 유지, 월간 고배당·저PB 리레이팅 수급 유입</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13228,7 +13667,7 @@
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>315.7</v>
+        <v>316.9</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
@@ -13244,14 +13683,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>(전일) 젠서은행(국유 대형은행): 7/28 A주 역대 신고가·600억 2차자본채 발행 후 고배당 수급 지속, 신고가 보합</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13283,7 +13722,7 @@
         <v>-6.84</v>
       </c>
       <c r="H5" t="n">
-        <v>168.2</v>
+        <v>168.8</v>
       </c>
       <c r="I5" t="n">
         <v>15.7</v>
@@ -13297,10 +13736,10 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13332,7 +13771,7 @@
         <v>-9.15</v>
       </c>
       <c r="H6" t="n">
-        <v>157.5</v>
+        <v>158.1</v>
       </c>
       <c r="I6" t="n">
         <v>21.9</v>
@@ -13346,14 +13785,10 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
-        </is>
-      </c>
+      <c r="M6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13385,7 +13820,7 @@
         <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>150.5</v>
+        <v>151</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
@@ -13397,14 +13832,14 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>(전일) (우량 주식은행·자오상은행): 기술주 대피 자금이 고배당 은행주로 이동, 배당 매력에 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13436,7 +13871,7 @@
         <v>-9.109999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>106.5</v>
+        <v>106.9</v>
       </c>
       <c r="I8" t="n">
         <v>91</v>
@@ -13450,10 +13885,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13485,7 +13920,7 @@
         <v>2.23</v>
       </c>
       <c r="H9" t="n">
-        <v>96.3</v>
+        <v>96.7</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
@@ -13501,14 +13936,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>(전일) (가전 대표주·메이디그룹): 이구환신 수혜 기대·기술섹터 폭락 반사 순환매로 신고가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13540,7 +13975,7 @@
         <v>3.24</v>
       </c>
       <c r="H10" t="n">
-        <v>91.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
@@ -13552,14 +13987,10 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
-        </is>
-      </c>
+      <c r="M10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13591,7 +14022,7 @@
         <v>-11.89</v>
       </c>
       <c r="H11" t="n">
-        <v>86.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>19.5</v>
@@ -13605,14 +14036,10 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
-        </is>
-      </c>
+      <c r="M11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13644,7 +14071,7 @@
         <v>1.95</v>
       </c>
       <c r="H12" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
@@ -13656,10 +14083,10 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="11" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13691,7 +14118,7 @@
         <v>2.74</v>
       </c>
       <c r="H13" t="n">
-        <v>58.1</v>
+        <v>58.4</v>
       </c>
       <c r="I13" t="n">
         <v>5.5</v>
@@ -13705,14 +14132,10 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
-        </is>
-      </c>
+      <c r="M13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13744,7 +14167,7 @@
         <v>-10</v>
       </c>
       <c r="H14" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="I14" t="n">
         <v>28.9</v>
@@ -13758,14 +14181,14 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>(전일) 둥산징미(PCB·광모듈): CPO·1.6T 광모듈 가격급락 루머+회사 단가하락 발언, CPO/PCB 연속 하한가권</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13797,7 +14220,7 @@
         <v>4.63</v>
       </c>
       <c r="H15" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
@@ -13809,14 +14232,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
-        </is>
-      </c>
+      <c r="M15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13848,7 +14267,7 @@
         <v>-4.35</v>
       </c>
       <c r="H16" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
@@ -13860,14 +14279,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>(전일) (국산 GPU·무어스레드): AI 하드웨어 섹터 전반 폭락 속 고평가 국산 GPU주 동반 급락</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13899,7 +14318,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
       <c r="I17" t="n">
         <v>10.4</v>
@@ -13913,10 +14332,10 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="11" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13948,7 +14367,7 @@
         <v>1.97</v>
       </c>
       <c r="H18" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
@@ -13960,14 +14379,14 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>(전일) 거리전기(에어컨 제조): AI·반도체주 급락 속 대소비재 역방향 강세, 이구환신(가전 교체보조) 확대 기대</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13999,7 +14418,7 @@
         <v>2.93</v>
       </c>
       <c r="H19" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="I19" t="n">
         <v>5.7</v>
@@ -14013,14 +14432,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
-        </is>
-      </c>
+      <c r="M19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14052,7 +14467,7 @@
         <v>-9.970000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="I20" t="n">
         <v>34.3</v>
@@ -14066,10 +14481,10 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14101,7 +14516,7 @@
         <v>-8.27</v>
       </c>
       <c r="H21" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="I21" t="n">
         <v>24.4</v>
@@ -14115,10 +14530,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14150,7 +14565,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
@@ -14162,10 +14577,10 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14197,7 +14612,7 @@
         <v>1.26</v>
       </c>
       <c r="H23" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
@@ -14209,14 +14624,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>(전일) (가전 대형주·하이얼스마트홈): 이구환신 정책 수혜·기술주 급락 반사 방어주 순환매로 신고가</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14248,7 +14663,7 @@
         <v>-10.54</v>
       </c>
       <c r="H24" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="I24" t="n">
         <v>15.2</v>
@@ -14266,14 +14681,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>(전일) 성훙커지A(PCB): 둥산징미 등 CPO 섹터 연속 급락 여파로 PCB 개념주 동반 하락, 섹터 수급 이탈</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14305,7 +14720,7 @@
         <v>-12.08</v>
       </c>
       <c r="H25" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="I25" t="n">
         <v>37.8</v>
@@ -14319,14 +14734,14 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14358,7 +14773,7 @@
         <v>-9</v>
       </c>
       <c r="H26" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
@@ -14374,14 +14789,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
-        </is>
-      </c>
+      <c r="M26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14413,7 +14824,7 @@
         <v>2.59</v>
       </c>
       <c r="H27" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
@@ -14425,14 +14836,14 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>(전일) 중궈중처(철도차량 제조): 2Q 신규수주 516억위안(2025매출 18.9%) 모멘텀 지속, 대소비재 강세 속 신고가</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14464,7 +14875,7 @@
         <v>-17.2</v>
       </c>
       <c r="H28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
@@ -14476,14 +14887,10 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
-        </is>
-      </c>
+      <c r="M28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14515,7 +14922,7 @@
         <v>-6.76</v>
       </c>
       <c r="H29" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="I29" t="n">
         <v>26.3</v>
@@ -14529,14 +14936,14 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>(전일) (광섬유 제조·창페이광섬유): 6월 고점 이후 광통신 섹터 조정 지속, 신규 촉매 없이 약세 연장</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14568,7 +14975,7 @@
         <v>1.45</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
@@ -14580,14 +14987,10 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
-        </is>
-      </c>
+      <c r="M30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14619,7 +15022,7 @@
         <v>-5.13</v>
       </c>
       <c r="H31" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
@@ -14631,14 +15034,14 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>(전일) (광섬유 광케이블·헝퉁광전): AI 연산 수요 불확실·한국 광통신주 동반 하락으로 급락</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14670,7 +15073,7 @@
         <v>-7.88</v>
       </c>
       <c r="H32" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
@@ -14682,10 +15085,10 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="11" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14729,10 +15132,10 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="11" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14764,7 +15167,7 @@
         <v>-11.36</v>
       </c>
       <c r="H34" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
@@ -14776,14 +15179,14 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="11" t="inlineStr">
-        <is>
-          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14815,7 +15218,7 @@
         <v>-8.539999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
@@ -14827,10 +15230,10 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="11" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14874,10 +15277,10 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="11" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14909,7 +15312,7 @@
         <v>-4.64</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="I37" t="n">
         <v>33.5</v>
@@ -14923,10 +15326,10 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="11" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14958,7 +15361,7 @@
         <v>-10</v>
       </c>
       <c r="H38" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="I38" t="n">
         <v>23.3</v>
@@ -14972,10 +15375,10 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="11" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15007,7 +15410,7 @@
         <v>-2.28</v>
       </c>
       <c r="H39" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="I39" t="n">
         <v>16.7</v>
@@ -15021,10 +15424,10 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="11" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15068,10 +15471,10 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="11" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15103,7 +15506,7 @@
         <v>-3.25</v>
       </c>
       <c r="H41" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="I41" t="n">
         <v>22.7</v>
@@ -15121,10 +15524,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="11" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15168,14 +15571,14 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="11" t="inlineStr">
-        <is>
-          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15223,14 +15626,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>(전일) (우주·특수전원): 상장 초 급등 후 조정 지속, 신규 재료 없음(IPO 거품 해소)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15276,10 +15679,10 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="11" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15311,7 +15714,7 @@
         <v>-2.96</v>
       </c>
       <c r="H45" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
@@ -15323,14 +15726,14 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>(전일) 중차이커지(유리섬유·AI전자포): 유상증자(44.8억위안) 희석 우려+AI하드웨어 조정 지속, 과창50 -4% 여파 신저가</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15374,10 +15777,10 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="11" t="inlineStr"/>
+      <c r="M46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15409,7 +15812,7 @@
         <v>-12.56</v>
       </c>
       <c r="H47" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I47" t="n">
         <v>235.5</v>
@@ -15423,14 +15826,10 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="11" t="inlineStr">
-        <is>
-          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
-        </is>
-      </c>
+      <c r="M47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15474,7 +15873,7 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="11" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M48"/>

--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -618,40 +618,47 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 오늘 새벽 마감한 미장은 실적 서프라이즈발 불반등(나스닥 +2.78%), 반면 직전 마감 중화권은 AI하드웨어 급락 vs 은행 순환매로 정반대 국면 — 같은 날 안에서 지역 디커플링.</t>
+          <t>💬 ■ 결론: 오늘 새벽 미장은 실적발 불반등(나스닥 +2.78%)인데 직전 마감 중화권은 AI하드웨어 폭락 vs 은행·소비 순환매 — 같은 AI 트레이드가 지역별로 정반대로 갈린 디커플링 국면.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ 美(한국시간 7/31 새벽 마감, 현지 7/30장): 나스닥 +2.78%·S&amp;P +1.66%·다우 +1.19%. 강세 금융(순강도+10, 12MF PER 15.3)·헬스(+6, 20.0배)로 CORT +27%·REGN·ILMN 실적 호조, XLK +5.5%. 약세는 Producer Manufacturing(-7, 23.9배)·CH로빈슨 -15%(배상판결)·알트리아 -9%·L3해리스 -8.6%. 메타는 AI지출로 잉여현금 -91%에 -8%.</t>
+          <t>■ 美(한국시간 7/31 새벽 마감, 현지 7/30장): 나스닥 +2.78%·S&amp;P +1.66%·다우 +1.19%. 강세 금융(순강도+10, 12MF PER 15.3배)·헬스(+6, 20.0배), XLK +5.5%로 메가캡 주도. 약세 XLC -2.7%(메타 -8%, AI지출로 잉여현금 -91%)·XLP -2.2%(알트리아 -9%)·Producer Manufacturing(-7). CH로빈슨 -15%(배상판결)·L3해리스 -8.6% 신저가.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 日(7/30 마감): 은행ETF -3.4%·자동차 -2.2% 약세 우위, 전기정밀 +2.5%. NEC 1분기 순익 2.6배로 +8%, 마키타 관세환급 일회성에 -10%, 키오시아 메모리 피크아웃 우려 신저가.</t>
+          <t>■ 日(7/30 마감): 닛케이 -1.49%. 은행ETF -3.4%·자동차 -2.2% 약세, 전기정밀 +2.5%. NEC 1분기 순익 2.6배로 +8%, 마키타 관세환급 일회성에 -10%, 키오시아 메모리 피크아웃 우려 신저가.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ 中·홍콩(7/30 마감): 상해 -0.62%·CSI300 -1.10%·항셍테크 -1.25%. 은행(中 순강도+9 PER 6.3배, 홍 +7 11.4배) 고배당 순환매 신고가 vs 전자기술(中 -16 30.3배, 홍 -6) 급락. 중지쉬촹 홍콩 IPO 첫날 붕괴가 광모듈 연쇄 급락 촉발, 중신궈지 -7.7%.</t>
+          <t>■ 中: 상해 -0.62%·CSI300 -1.10%. AI하드웨어 붕괴가 핵심 — 5G통신ETF -7.8%·반도체 -6.7%(1M -34.9)·테크 -5.1%, 전자기술 순강도 -16(12MF PER 30.3배). 반대편은 백주 +3.7%·소비 +2.9%·은행 +2.6%(순강도+9, PER 6.3배) 방어 순환매. 촉매는 중지쉬촹 홍콩 IPO 첫날 붕괴 → 광모듈 연쇄 급락.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①미 불반등이 중화권 AI하드웨어로 전이될지(오늘 아시아장 관전) ②광모듈 밸류 조정 지속 여부 ③은행 방어 순환매 지속성.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+          <t>■ 홍콩: 항셍 +0.20%·항셍테크 -1.25%. H주ETF +1.4%로 은행(순강도+7, PER 11.4배) 신고가 주도, 반면 중신궈지 -7.7% 등 전자기술 -6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①미 불반등이 오늘 아시아 AI하드웨어로 전이될지 ②반도체ETF YTD +30.9% 남은 되돌림 여지 ③은행·소비 방어 순환매 지속성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -3865,7 +3872,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>메가캡 테크 실적 서프라이즈로 당일 +5.5% 급등, 다만 전자기술 순강도 -2로 breadth는 대형주 편중</t>
+          <t>메가캡 실적 서프라이즈로 +5.5% 급등, 다만 전자기술 순강도 -2로 breadth는 대형주 편중</t>
         </is>
       </c>
       <c r="E2" s="9" t="n">
@@ -3941,7 +3948,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>CORT +27%·REGN·ILMN 개별 실적주 강세, 다만 ALNY -28% 미스 혼재로 ETF -1.6%</t>
+          <t>CORT +27%·REGN·ILMN 개별 실적주 강세, ALNY -28% 미스 혼재로 ETF는 -1.6%</t>
         </is>
       </c>
       <c r="E3" s="9" t="n">
@@ -4017,7 +4024,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>신고-신저 순강도 +10 전 섹터 최강, 은행·보험 신고가 다수로 가치·방어 선호(+0.6%)</t>
+          <t>+0.6%, 순강도 +10 전 섹터 최강·12MF PER 15.3배로 가치·방어 선호 지속</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
@@ -4093,7 +4100,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>치폴레 +12.5% 등 외식·서비스 실적 개선에 당일 +0.7%</t>
+          <t>+0.7%, 치폴레 +12.5% 등 외식·서비스 실적 개선이 견인</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
@@ -4169,7 +4176,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>당일 -2.7%로 전 섹터 최약, 광고·미디어 대형주 실적 경계</t>
+          <t>-2.7%로 당일 최약, 메타 -8%(AI지출로 잉여현금 -91%)가 직접 타격</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
@@ -4245,7 +4252,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>ETF +1.0%에도 Producer Manufacturing 순강도 -7로 breadth 약세, 방산 L3해리스 -8.6% 신저가</t>
+          <t>+1.0%이나 Producer Manufacturing 순강도 -7로 breadth 취약, L3해리스 -8.6% 신저가</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -4321,7 +4328,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>담배 알트리아 -9.3% 실적 실망 등으로 당일 -2.2% 약세</t>
+          <t>-2.2%, 알트리아 -9.3% 실적 실망이 필수소비재 전반 압박</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
@@ -4397,7 +4404,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>1개월 +11%로 상대강세 지속, 당일 +0.5%</t>
+          <t>+0.5%, 1개월 +11.0%로 상대강세 지속</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -4473,7 +4480,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>당일 -0.6% 소폭 약세, 뚜렷한 촉매 없음</t>
+          <t>-0.6%, 1주 -3.3%로 금리 민감 방어주 소외</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -4549,7 +4556,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>당일 -0.2% 보합권, 방향성 부재</t>
+          <t>-0.2% 보합권, 방향성 부재</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -4625,7 +4632,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>ETF -1.4% 약세이나 JLL +6.4% 실적 서프라이즈로 52주 신고가 개별 차별화</t>
+          <t>-1.4%이나 JLL +6.4% 실적 서프라이즈로 52주 신고가 개별 차별화</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -5923,7 +5930,11 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>+0.3%(1M +13.2), 항셍 대형주 은행 주도로 견조</t>
+        </is>
+      </c>
       <c r="E30" s="9" t="n">
         <v>0.3</v>
       </c>
@@ -5995,7 +6006,11 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>+1.4%(1M +16.3)로 홍콩 3종 중 최강, H주 은행 신고가 수혜</t>
+        </is>
+      </c>
       <c r="E31" s="9" t="n">
         <v>1.4</v>
       </c>
@@ -6067,7 +6082,11 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>-1.0%(YTD26 -12.5), 항셍테크는 반도체 조정에 동반 약세</t>
+        </is>
+      </c>
       <c r="E32" s="9" t="n">
         <v>-1</v>
       </c>
@@ -6137,7 +6156,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 전자기술 순강도 -16 최약, 광모듈·반도체 신저가 속출로 약세 추정</t>
+          <t>-6.7%(1주 -13.4·1M -34.9) 급락, 다만 YTD26 +30.9%로 섹터 1위 — 급등 후 되돌림 성격</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
@@ -6213,7 +6232,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 기술주 전반 약세, 광모듈·반도체 조정에 약세 추정</t>
+          <t>-5.1%(1M -29.9), 광모듈·반도체 조정이 기술주 전반으로 확산</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
@@ -6289,7 +6308,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 광통신·부품 약세 연동 추정(통신 순강도 중립)</t>
+          <t>-7.8%로 당일 최약(1M -34.0), 광통신 체인 붕괴가 직격</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
@@ -6365,7 +6384,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 소비내구재 순강도 +2 강세, 신에너지차 상대 견조 추정</t>
+          <t>-0.1% 보합, 기술주 급락장에서 상대적 방어</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
@@ -6437,7 +6456,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 제조업 breadth 약세, 방산 뚜렷한 촉매 없음 추정</t>
+          <t>-1.9%(YTD26 -21.8로 13개 중 최하위), 방산 소외 지속</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
@@ -6513,7 +6532,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 신재생·제조 breadth 약세 추정</t>
+          <t>-1.5%(1M -21.5), 태양광 약세 지속</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
@@ -6585,7 +6604,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 소비 중립, 방향성 부재 추정</t>
+          <t>+3.7%(1M +13.6)로 당일 최강, 백주·소비로 자금 순환</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
@@ -6661,7 +6680,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 금융 순강도 +9 최강, 은행 고배당 순환매로 신고가 다수 강세 추정</t>
+          <t>+2.6%(1M +14.0), 순강도 +9·12MF PER 6.3배 저평가 고배당 순환매로 신고가 다수</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
@@ -6737,7 +6756,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 비철금속 순강도 -2 약세 추정</t>
+          <t>-1.2%(3M -14.5), 비철 약세 지속</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
@@ -6813,7 +6832,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 부동산 뚜렷한 촉매 없음 추정</t>
+          <t>-0.3% 보합, 부동산 촉매 부재</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
@@ -6889,7 +6908,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 금융 강세 흐름 일부 수혜 추정, 증권 개별 촉매 미확인</t>
+          <t>0.0% 보합, 은행 강세에도 증권은 소외</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
@@ -6965,7 +6984,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 의약 중립, 방향성 부재 추정</t>
+          <t>+0.8%(1M +4.7), 의약 완만한 방어 흐름</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
@@ -7041,7 +7060,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>당일 ETF 시세 수집 실패(공란). 소비 중립, 방어주 선호 일부 추정</t>
+          <t>+2.9%(1M +11.0), 소비 방어주 선호로 백주와 동반 강세</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
@@ -7379,7 +7398,11 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -7577,7 +7600,11 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7732,7 +7759,11 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -7983,7 +8014,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -8081,7 +8116,11 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8236,7 +8275,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -8289,7 +8332,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8697,7 +8744,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8899,7 +8950,11 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9054,7 +9109,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -9305,7 +9364,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="10" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -9464,7 +9527,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -9774,7 +9841,7 @@
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
+          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9896,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="10" t="inlineStr"/>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -10636,7 +10707,11 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -10885,7 +10960,11 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -11146,7 +11225,11 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -11503,7 +11586,11 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -11862,7 +11949,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -11911,7 +12002,11 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M29"/>
@@ -12114,7 +12209,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -12263,7 +12362,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
+          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12576,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -12630,7 +12733,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -12681,7 +12788,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
+          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13116,11 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -13062,7 +13173,7 @@
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
+          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13495,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13433,7 +13548,11 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M28"/>
@@ -13785,7 +13904,11 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -13987,7 +14110,11 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -14036,7 +14163,11 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14132,7 +14263,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -14232,7 +14367,11 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -14432,7 +14571,11 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -14736,7 +14879,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
+          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14932,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -14887,7 +15034,11 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -14987,7 +15138,11 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -15181,7 +15336,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
+          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15728,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
+          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15981,11 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">

--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -17,11 +17,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중국A" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$I$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$M$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$M$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$M$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$M$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$K$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$N$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$N$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$N$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -868,29 +868,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61434.19</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>-1.49</v>
+        <v>61988.4</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.9</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-7.08</v>
+        <v>-6.68</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-11.56</v>
+        <v>-11.52</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>22.04</v>
+        <v>23.14</v>
       </c>
       <c r="I5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1069,6 +1069,8 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1114,6 +1116,16 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>12MF표본수</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PER(TTM중앙값)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PBR(중앙값)</t>
         </is>
       </c>
@@ -1150,6 +1162,12 @@
         <v>15.3</v>
       </c>
       <c r="I2" t="n">
+        <v>161</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K2" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -1185,6 +1203,12 @@
         <v>20</v>
       </c>
       <c r="I3" t="n">
+        <v>56</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="K3" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -1220,6 +1244,12 @@
         <v>21.5</v>
       </c>
       <c r="I4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -1255,6 +1285,12 @@
         <v>15.9</v>
       </c>
       <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1290,6 +1326,12 @@
         <v>16.9</v>
       </c>
       <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1325,6 +1367,12 @@
         <v>22.7</v>
       </c>
       <c r="I7" t="n">
+        <v>84</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="K7" t="n">
         <v>6.6</v>
       </c>
     </row>
@@ -1360,6 +1408,12 @@
         <v>18.6</v>
       </c>
       <c r="I8" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -1395,6 +1449,12 @@
         <v>16.6</v>
       </c>
       <c r="I9" t="n">
+        <v>34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -1430,6 +1490,12 @@
         <v>28.8</v>
       </c>
       <c r="I10" t="n">
+        <v>87</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K10" t="n">
         <v>7.9</v>
       </c>
     </row>
@@ -1465,6 +1531,12 @@
         <v>23.3</v>
       </c>
       <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="K11" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -1500,6 +1572,12 @@
         <v>17.2</v>
       </c>
       <c r="I12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -1535,6 +1613,12 @@
         <v>20.1</v>
       </c>
       <c r="I13" t="n">
+        <v>31</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K13" t="n">
         <v>8.4</v>
       </c>
     </row>
@@ -1570,6 +1654,12 @@
         <v>21.3</v>
       </c>
       <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -1605,6 +1695,12 @@
         <v>23.9</v>
       </c>
       <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K15" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -1640,6 +1736,12 @@
         <v>19.8</v>
       </c>
       <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K16" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -1675,6 +1777,12 @@
         <v>13.8</v>
       </c>
       <c r="I17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -1710,6 +1818,12 @@
         <v>19.6</v>
       </c>
       <c r="I18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="K18" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -1745,6 +1859,12 @@
         <v>9.9</v>
       </c>
       <c r="I19" t="n">
+        <v>22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -1776,10 +1896,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>30.5</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54</v>
+      </c>
+      <c r="K20" t="n">
         <v>9.6</v>
       </c>
     </row>
@@ -1815,6 +1939,12 @@
         <v>15.7</v>
       </c>
       <c r="I21" t="n">
+        <v>22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1846,10 +1976,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -1885,6 +2019,12 @@
         <v>13.8</v>
       </c>
       <c r="I23" t="n">
+        <v>11</v>
+      </c>
+      <c r="J23" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K23" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -1916,10 +2056,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>31.6</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="K24" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -1951,10 +2095,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -1986,10 +2134,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>30.5</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K26" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -2025,6 +2177,12 @@
         <v>19.9</v>
       </c>
       <c r="I27" t="n">
+        <v>18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -2060,6 +2218,12 @@
         <v>11.2</v>
       </c>
       <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>12</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2095,6 +2259,12 @@
         <v>30.6</v>
       </c>
       <c r="I29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -2126,10 +2296,14 @@
           <t>약세</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2165,6 +2339,12 @@
         <v>15.4</v>
       </c>
       <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K31" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -2196,10 +2376,14 @@
           <t>약세</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K32" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -2231,10 +2415,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K33" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -2266,10 +2454,14 @@
           <t>혼조</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K34" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -2301,10 +2493,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K35" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -2336,10 +2532,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K36" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2375,6 +2575,12 @@
         <v>14.3</v>
       </c>
       <c r="I37" t="n">
+        <v>25</v>
+      </c>
+      <c r="J37" t="n">
+        <v>16</v>
+      </c>
+      <c r="K37" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -2410,6 +2616,12 @@
         <v>20.3</v>
       </c>
       <c r="I38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K38" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -2441,12 +2653,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>2</v>
       </c>
+      <c r="J39" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2480,6 +2696,12 @@
         <v>11.4</v>
       </c>
       <c r="I40" t="n">
+        <v>28</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K40" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -2515,6 +2737,12 @@
         <v>18.1</v>
       </c>
       <c r="I41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2550,6 +2778,12 @@
         <v>12.3</v>
       </c>
       <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="K42" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -2585,6 +2819,12 @@
         <v>13.7</v>
       </c>
       <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K43" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -2620,6 +2860,12 @@
         <v>11.3</v>
       </c>
       <c r="I44" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K44" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -2651,10 +2897,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K45" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2690,6 +2940,12 @@
         <v>14.9</v>
       </c>
       <c r="I46" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K46" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -2721,10 +2977,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>15.3</v>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K47" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -2760,6 +3020,12 @@
         <v>13.8</v>
       </c>
       <c r="I48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K48" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2795,6 +3061,12 @@
         <v>17.2</v>
       </c>
       <c r="I49" t="n">
+        <v>12</v>
+      </c>
+      <c r="J49" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K49" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -2826,10 +3098,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K50" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2861,10 +3137,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K51" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -2896,10 +3176,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" t="n">
-        <v>7</v>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="K52" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -2935,6 +3219,12 @@
         <v>32.6</v>
       </c>
       <c r="I53" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="K53" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -2966,10 +3256,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -3005,6 +3299,12 @@
         <v>8.5</v>
       </c>
       <c r="I55" t="n">
+        <v>6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K55" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -3036,10 +3336,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K56" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -3075,6 +3379,12 @@
         <v>12</v>
       </c>
       <c r="I57" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K57" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -3110,6 +3420,12 @@
         <v>6.3</v>
       </c>
       <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K58" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -3141,10 +3457,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H59" t="n">
-        <v>20.8</v>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K59" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -3176,10 +3496,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H60" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K60" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -3211,10 +3535,14 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H61" t="n">
-        <v>19.6</v>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K61" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -3248,6 +3576,10 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -3279,10 +3611,14 @@
           <t>약세</t>
         </is>
       </c>
-      <c r="H63" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="K63" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -3314,10 +3650,14 @@
           <t>약세</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K64" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -3353,6 +3693,12 @@
         <v>65.40000000000001</v>
       </c>
       <c r="I65" t="n">
+        <v>8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="K65" t="n">
         <v>7.7</v>
       </c>
     </row>
@@ -3388,6 +3734,12 @@
         <v>29.2</v>
       </c>
       <c r="I66" t="n">
+        <v>17</v>
+      </c>
+      <c r="J66" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="K66" t="n">
         <v>4.7</v>
       </c>
     </row>
@@ -3423,6 +3775,12 @@
         <v>30.3</v>
       </c>
       <c r="I67" t="n">
+        <v>38</v>
+      </c>
+      <c r="J67" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K67" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3456,6 +3814,12 @@
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K68" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -3489,6 +3853,12 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K69" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -3522,6 +3892,12 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K70" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -3553,10 +3929,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H71" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K71" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -3588,10 +3968,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H72" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>25</v>
+      </c>
+      <c r="K72" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -3627,6 +4011,12 @@
         <v>30.1</v>
       </c>
       <c r="I73" t="n">
+        <v>9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="K73" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -3660,6 +4050,12 @@
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K74" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -3693,18 +4089,22 @@
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>※ PER=12개월 선행(12MF, 컨센서스 기준), PBR=최근분기 순자산 — 섹터 유니버스($10B+) 중앙값, 적자 제외</t>
+          <t>※ PER(12MF)=선행 컨센서스 기준, 12MF표본수=그 중앙값을 만든 종목 수 (표본 5개 미만은 오도 방지를 위해 공란). 중국A는 선행 추정 커버리지가 34% 수준이라 TTM 중앙값을 함께 보고 판단할 것. PBR=최근분기 순자산 — 모두 섹터 유니버스($10B+) 중앙값, 적자 제외</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:K75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5215,13 +5615,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>-6.3</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>14.5</v>
@@ -5644,16 +6044,16 @@
       </c>
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="9" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>7.4</v>
@@ -7268,7 +7668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7280,10 +7680,11 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7334,20 +7735,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>PER(TTM)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>60일</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>52주</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>이유</t>
         </is>
@@ -7391,18 +7797,17 @@
       <c r="I2" t="n">
         <v>17.4</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
-        </is>
-      </c>
+      <c r="J2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -7443,15 +7848,18 @@
         <v>27.3</v>
       </c>
       <c r="J3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K3" t="n">
         <v>76.2</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -7492,15 +7900,18 @@
         <v>15.9</v>
       </c>
       <c r="J4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>5.8</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7541,19 +7952,22 @@
         <v>10.5</v>
       </c>
       <c r="J5" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>6.6</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7593,18 +8007,17 @@
       <c r="I6" t="n">
         <v>11.7</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
-        </is>
-      </c>
+      <c r="J6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7644,20 +8057,21 @@
       <c r="I7" t="n">
         <v>140.1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>53.3</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 스노우플레이크(클라우드 데이터플랫폼): 웰스파고 목표가 $320→$500 상향·AI에이전트 지출 가속 논거</t>
         </is>
@@ -7702,15 +8116,18 @@
         <v>33.9</v>
       </c>
       <c r="J8" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K8" t="n">
         <v>15</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7751,19 +8168,18 @@
         <v>13.2</v>
       </c>
       <c r="J9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -7804,15 +8220,18 @@
         <v>32</v>
       </c>
       <c r="J10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K10" t="n">
         <v>11</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7853,15 +8272,18 @@
         <v>18.2</v>
       </c>
       <c r="J11" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7902,15 +8324,18 @@
         <v>15.3</v>
       </c>
       <c r="J12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.8</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7951,19 +8376,22 @@
         <v>23.8</v>
       </c>
       <c r="J13" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="K13" t="n">
         <v>7.8</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -8003,22 +8431,21 @@
       <c r="I14" t="n">
         <v>22</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J14" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -8059,15 +8486,18 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8108,19 +8538,18 @@
         <v>30.4</v>
       </c>
       <c r="J16" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K16" t="n">
         <v>22.2</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8161,19 +8590,22 @@
         <v>10.9</v>
       </c>
       <c r="J17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8214,15 +8646,18 @@
         <v>16.2</v>
       </c>
       <c r="J18" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K18" t="n">
         <v>4</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8263,23 +8698,22 @@
         <v>36.8</v>
       </c>
       <c r="J19" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="K19" t="n">
         <v>11.6</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -8320,23 +8754,22 @@
         <v>22.4</v>
       </c>
       <c r="J20" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="K20" t="n">
         <v>25.5</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8377,15 +8810,18 @@
         <v>22.8</v>
       </c>
       <c r="J21" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.3</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -8426,15 +8862,18 @@
         <v>12.4</v>
       </c>
       <c r="J22" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.4</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전서비스): 실적 상회에도 에너지 섹터 약세·유가 불확실성으로 하락</t>
         </is>
@@ -8479,19 +8918,22 @@
         <v>16.9</v>
       </c>
       <c r="J23" t="n">
+        <v>28</v>
+      </c>
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8532,19 +8974,22 @@
         <v>25.8</v>
       </c>
       <c r="J24" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="K24" t="n">
         <v>8.4</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -8585,15 +9030,18 @@
         <v>21.4</v>
       </c>
       <c r="J25" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.2</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -8634,15 +9082,18 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K26" t="n">
         <v>1.2</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -8683,15 +9134,18 @@
         <v>19.9</v>
       </c>
       <c r="J27" t="n">
+        <v>43</v>
+      </c>
+      <c r="K27" t="n">
         <v>50.2</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -8731,24 +9185,21 @@
       <c r="I28" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
         <v>4.6</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8789,19 +9240,22 @@
         <v>92.3</v>
       </c>
       <c r="J29" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.2</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -8842,19 +9296,22 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K30" t="n">
         <v>5.5</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -8895,15 +9352,18 @@
         <v>13.3</v>
       </c>
       <c r="J31" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.2</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -8943,18 +9403,17 @@
       <c r="I32" t="n">
         <v>21.3</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
-        </is>
-      </c>
+      <c r="J32" t="n">
+        <v>28</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -8995,19 +9454,22 @@
         <v>25.2</v>
       </c>
       <c r="J33" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="K33" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -9047,16 +9509,17 @@
       <c r="I34" t="n">
         <v>21.5</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
         <v>4.9</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -9097,23 +9560,22 @@
         <v>14.8</v>
       </c>
       <c r="J35" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="K35" t="n">
         <v>2.3</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -9154,15 +9616,18 @@
         <v>13.1</v>
       </c>
       <c r="J36" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="K36" t="n">
         <v>1.9</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -9203,19 +9668,22 @@
         <v>25.7</v>
       </c>
       <c r="J37" t="n">
+        <v>18</v>
+      </c>
+      <c r="K37" t="n">
         <v>2.8</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="10" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -9255,16 +9723,17 @@
       <c r="I38" t="n">
         <v>63.5</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
         <v>2.9</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -9302,16 +9771,17 @@
         <v>14.6</v>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
         <v>4.9</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -9351,24 +9821,21 @@
       <c r="I40" t="n">
         <v>24.4</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
         <v>1316.2</v>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="10" t="inlineStr">
-        <is>
-          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -9409,19 +9876,22 @@
         <v>16.7</v>
       </c>
       <c r="J41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K41" t="n">
         <v>11.1</v>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>(전일) 레녹스인터내셔널(주거용 HVAC): 2Q매출 소폭 미달·FY EPS가이던스 $23.50으로 하향(컨센 -4.7%)</t>
         </is>
@@ -9466,15 +9936,18 @@
         <v>27.7</v>
       </c>
       <c r="J42" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K42" t="n">
         <v>2.9</v>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -9514,24 +9987,21 @@
       <c r="I43" t="n">
         <v>13</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
         <v>2.3</v>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -9572,15 +10042,18 @@
         <v>21.5</v>
       </c>
       <c r="J44" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K44" t="n">
         <v>9.1</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -9621,19 +10094,22 @@
         <v>30.9</v>
       </c>
       <c r="J45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K45" t="n">
         <v>9</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>(전일) (캐주얼다이닝): 다수 증권사 목표가 상향(웰스파고 $220)·소고기값 완화 기대</t>
         </is>
@@ -9678,15 +10154,18 @@
         <v>15.3</v>
       </c>
       <c r="J46" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K46" t="n">
         <v>4</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>(전일) (산업용 바코드·모바일컴퓨터): 소프트웨어·AI분석 수요 회복 기대, 목표가 연속 상향으로 신고가</t>
         </is>
@@ -9731,15 +10210,18 @@
         <v>16.7</v>
       </c>
       <c r="J47" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K47" t="n">
         <v>5.8</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -9779,16 +10261,17 @@
       <c r="I48" t="n">
         <v>24.4</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -9828,20 +10311,23 @@
       <c r="I49" t="n">
         <v>25.3</v>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J49" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M49" s="10" t="inlineStr">
-        <is>
-          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
         </is>
       </c>
     </row>
@@ -9884,23 +10370,22 @@
         <v>32.4</v>
       </c>
       <c r="J50" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="K50" t="n">
         <v>18.1</v>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="10" t="inlineStr">
-        <is>
-          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -9940,18 +10425,21 @@
       <c r="I51" t="n">
         <v>24.7</v>
       </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J51" t="n">
+        <v>27</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓스코(HVAC유통): 2Q EPS $4.00 컨센 $4.39 미달·매출총이익률 27.5%로 전년比 축소</t>
         </is>
@@ -9993,16 +10481,17 @@
         <v>12.2</v>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
         <v>6.4</v>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -10042,14 +10531,17 @@
       <c r="I53" t="n">
         <v>16.2</v>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="J53" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>(전일) 에버코어(독립자문 투자은행): 2Q EPS 소폭 상회했으나 1Q 역대최고 대비 실망·'뉴스에 팔자'</t>
         </is>
@@ -10094,15 +10586,18 @@
         <v>10.2</v>
       </c>
       <c r="J54" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K54" t="n">
         <v>2.5</v>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -10143,19 +10638,22 @@
         <v>19.6</v>
       </c>
       <c r="J55" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K55" t="n">
         <v>7.6</v>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M55" s="10" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -10196,19 +10694,22 @@
         <v>10.9</v>
       </c>
       <c r="J56" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K56" t="n">
         <v>1.7</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M56" s="10" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -10249,19 +10750,22 @@
         <v>11</v>
       </c>
       <c r="J57" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K57" t="n">
         <v>1.4</v>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M57" s="10" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -10302,15 +10806,18 @@
         <v>18.9</v>
       </c>
       <c r="J58" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="K58" t="n">
         <v>4</v>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -10350,14 +10857,17 @@
       <c r="I59" t="n">
         <v>22.1</v>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -10398,19 +10908,22 @@
         <v>15</v>
       </c>
       <c r="J60" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="K60" t="n">
         <v>2.3</v>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M60" s="10" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -10451,22 +10964,25 @@
         <v>13</v>
       </c>
       <c r="J61" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K61" t="n">
         <v>4</v>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M61"/>
+  <autoFilter ref="A1:N61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10477,7 +10993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10489,10 +11005,11 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10543,20 +11060,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>PER(TTM)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>60일</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>52주</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>이유</t>
         </is>
@@ -10601,15 +11123,18 @@
         <v>42.5</v>
       </c>
       <c r="J2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K2" t="n">
         <v>1.5</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -10644,21 +11169,22 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>140.7</v>
+        <v>140.8</v>
       </c>
       <c r="I3" t="n">
         <v>18.6</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -10699,19 +11225,18 @@
         <v>3.9</v>
       </c>
       <c r="J4" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="K4" t="n">
         <v>15.4</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -10752,19 +11277,22 @@
         <v>29.7</v>
       </c>
       <c r="J5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>11.4</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -10805,19 +11333,22 @@
         <v>16.1</v>
       </c>
       <c r="J6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.3</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -10858,15 +11389,18 @@
         <v>25.1</v>
       </c>
       <c r="J7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.2</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -10905,15 +11439,18 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.3</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -10952,19 +11489,18 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -11005,15 +11541,18 @@
         <v>14.2</v>
       </c>
       <c r="J10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K10" t="n">
         <v>1.1</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) (자동차부품 1위): 7/31 결산 앞둔 기대매수, 日증시 반등 수혜</t>
         </is>
@@ -11058,15 +11597,18 @@
         <v>28.1</v>
       </c>
       <c r="J11" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K11" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) (디스코·반도체 다이싱장비): 7-9월 순이익 가이던스 395억엔이 컨센 473억엔 대폭 하회로 -12% 급락</t>
         </is>
@@ -11109,19 +11651,22 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K12" t="n">
         <v>1.4</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) (브리지스톤·타이어): 1Q 경상이익 +47% 호조, 8/7 결산 기대 매수로 52주 신고가</t>
         </is>
@@ -11164,15 +11709,18 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.4</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) (도쿄디즈니리조트): 입장권 상한 인상 보도·7/30 결산 기대로 연속 급등</t>
         </is>
@@ -11217,19 +11765,18 @@
         <v>19.2</v>
       </c>
       <c r="J14" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.3</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -11270,15 +11817,18 @@
         <v>30.6</v>
       </c>
       <c r="J15" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K15" t="n">
         <v>13.4</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 레이저테크(EUV 마스크검사장비): SK하이닉스 실적 미달+한국증시 서킷브레이커로 장비주 집중매도</t>
         </is>
@@ -11323,15 +11873,18 @@
         <v>21.5</v>
       </c>
       <c r="J16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K16" t="n">
         <v>5.2</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 코나미그룹(게임·헬스클럽 복합): 카프콤 1Q 영업익 +67% 호실적에 게임주 전반 동반매수</t>
         </is>
@@ -11376,15 +11929,18 @@
         <v>21.6</v>
       </c>
       <c r="J17" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.5</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) (게임·완구): 맥쿼리 목표주가 5500→5600엔 상향, 8/5 결산 기대매수</t>
         </is>
@@ -11427,15 +11983,18 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="K18" t="n">
         <v>7.4</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>(전일) (IT컨설팅·NRI): 7/30 결산 앞두고 기대 매수, FY27 이익 전망 개선으로 신고가</t>
         </is>
@@ -11480,15 +12039,18 @@
         <v>11.2</v>
       </c>
       <c r="J19" t="n">
+        <v>12</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.8</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -11527,15 +12089,18 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.1</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) (레조낙·반도체소재): 중국 노광장비 자체제조 보도·아시아 AI반도체 전반 급락 수급으로 신저가</t>
         </is>
@@ -11578,19 +12143,18 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.6</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -11629,15 +12193,18 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.1</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) (ERP·업무SW): 4-6월 순이익 16%↑ 결산 재평가, IT섹터로 자금 이동</t>
         </is>
@@ -11682,15 +12249,18 @@
         <v>9.9</v>
       </c>
       <c r="J23" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.7</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>(전일) 스바루(자동차): AI반도체 섹터 급락에 저배당·저PBR 자동차주로 자금이동</t>
         </is>
@@ -11732,16 +12302,17 @@
         <v>11.4</v>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -11782,15 +12353,18 @@
         <v>11.7</v>
       </c>
       <c r="J25" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.8</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -11831,19 +12405,22 @@
         <v>34.3</v>
       </c>
       <c r="J26" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>(전일) 시마노(자전거 부품·낚시): 2Q 순익 +606% 급증 호실적에 상반기 업적 상방수정</t>
         </is>
@@ -11888,15 +12465,18 @@
         <v>25.3</v>
       </c>
       <c r="J27" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K27" t="n">
         <v>10.5</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -11937,23 +12517,22 @@
         <v>25.6</v>
       </c>
       <c r="J28" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.8</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -11994,22 +12573,21 @@
         <v>31.6</v>
       </c>
       <c r="J29" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.9</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M29"/>
+  <autoFilter ref="A1:N29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12020,7 +12598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12032,10 +12610,11 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12086,20 +12665,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>PER(TTM)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>60일</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>52주</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>이유</t>
         </is>
@@ -12142,19 +12726,22 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.6</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 독립 촉매 없이 은행 섹터 전반 강세·위안화 강세 수급으로 52주 신고가</t>
         </is>
@@ -12197,23 +12784,22 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -12252,19 +12838,22 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.6</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -12303,15 +12892,18 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -12352,17 +12944,20 @@
         <v>45.3</v>
       </c>
       <c r="J6" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.9</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
         </is>
       </c>
     </row>
@@ -12403,19 +12998,22 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K7" t="n">
         <v>2.9</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) (가전·로봇): 자사주 매입 집행·휴머노이드 상업화 기대 매수세 유입으로 신고가</t>
         </is>
@@ -12459,16 +13057,17 @@
       <c r="I8" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>3.4</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) (음식배달·로컬커머스): 미이란 긴장 완화 리스크오프 해소·과기주 매수, 2Q 적자축소 기대</t>
         </is>
@@ -12513,15 +13112,18 @@
         <v>9.6</v>
       </c>
       <c r="J9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K9" t="n">
         <v>1.2</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) (손해보험·중국재보험): 배당지급일 직전 막차 매수 집중, 은행·보험 방어섹터 동반 강세로 신고가</t>
         </is>
@@ -12563,24 +13165,21 @@
         <v>31.5</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>7</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -12619,15 +13218,18 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K11" t="n">
         <v>1.5</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 하이얼스마트홈(가전 제조): 신소비·대형소비주 섹터 수급 유입 동반 강세(개별 촉매 미확인, 수급 추정)</t>
         </is>
@@ -12672,19 +13274,22 @@
         <v>16.2</v>
       </c>
       <c r="J12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K12" t="n">
         <v>1.8</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -12725,19 +13330,18 @@
         <v>4.8</v>
       </c>
       <c r="J13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.3</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -12778,17 +13382,20 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J14" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.7</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
         </is>
       </c>
     </row>
@@ -12830,20 +13437,21 @@
       <c r="I15" t="n">
         <v>12.2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
         <v>7.4</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 성훙테크H(AI서버 PCB): AI하드웨어 PCB 섹터 조정 지속·엔비디아 루빈 품질 루머 및 이익 정점 우려</t>
         </is>
@@ -12888,15 +13496,18 @@
         <v>12.9</v>
       </c>
       <c r="J16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="K16" t="n">
         <v>1.8</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 은하오락(마카오 카지노): 마카오 GGR 회복 기대·7월 일평균 매출 전주比 +9%·골드만 매수 유지</t>
         </is>
@@ -12938,20 +13549,21 @@
         <v>17.1</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
         <v>33.5</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 딩타이가오커(PCB 드릴비트 글로벌 1위): AI서버 PCB 섹터 전반 급락(광허테크 등 -16%)에 동반</t>
         </is>
@@ -12996,19 +13608,22 @@
         <v>12.3</v>
       </c>
       <c r="J18" t="n">
+        <v>47</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>(전일) (복합기업·부동산): UBS 목표가 20% 상향, 태고지산·캐세이퍼시픽 이익 기여 기대로 신고가</t>
         </is>
@@ -13053,19 +13668,22 @@
         <v>11.1</v>
       </c>
       <c r="J19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.1</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 스와이어퍼시픽B(항공·부동산·음료 복합): 특별한 뉴스 없음(시장 전반 상승 흐름 동반 추정)</t>
         </is>
@@ -13107,20 +13725,17 @@
         <v>15.2</v>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
         <v>29.1</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -13159,21 +13774,24 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.2</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
         </is>
       </c>
     </row>
@@ -13216,15 +13834,18 @@
         <v>10.8</v>
       </c>
       <c r="J22" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K22" t="n">
         <v>1.3</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) 텐센트뮤직(온라인음악 스트리밍): 항셍테크 +2.84%, 텐센트·비리비리 등 대형 인터넷주 동반 강세</t>
         </is>
@@ -13269,15 +13890,18 @@
         <v>11.3</v>
       </c>
       <c r="J23" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K23" t="n">
         <v>5.6</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>(전일) (동박적층판 PCB소재·젠타오): 엔비디아 차세대 AI서버랙 PCB 양산 2028년 연기 충격으로 -16% 급락</t>
         </is>
@@ -13322,15 +13946,18 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.7</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>(전일) (국제택배·물류): 자사주 매입 지속, 동남아 패키지 처리량 +84% 역대 최대로 신고가</t>
         </is>
@@ -13372,18 +13999,21 @@
         <v>12.4</v>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="J25" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) HKT트러스트(홍콩 통신): 7/30 중간 실적발표 앞두고 기대 매수 유입(+0.08% 소폭)</t>
         </is>
@@ -13428,19 +14058,22 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J26" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" t="n">
         <v>1.6</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>(전일) (홍콩 국적 항공사): 캐세이퍼시픽, 상반기 순이익 60~65억 홍콩달러(전년비 최대 +76%) 예고, 여객·화물 호조</t>
         </is>
@@ -13482,24 +14115,21 @@
         <v>10.6</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
         <v>2.2</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
-        <is>
-          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13539,23 +14169,20 @@
       <c r="I28" t="n">
         <v>12.2</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
         <v>0.4</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M28"/>
+  <autoFilter ref="A1:N28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13566,7 +14193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13578,10 +14205,11 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13632,20 +14260,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>PER(TTM)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>60일</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>52주</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>이유</t>
         </is>
@@ -13687,16 +14320,17 @@
         <v>401.2</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>0.7</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 창업판 급락 속 방어주 순환매로 은행섹터 강세, 공상은행 52주 신고가</t>
         </is>
@@ -13738,16 +14372,17 @@
         <v>353.2</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 농업은행(국유 대형은행): 섹터 선두 강세 후 신고가권 유지, 월간 고배당·저PB 리레이팅 수급 유입</t>
         </is>
@@ -13790,19 +14425,22 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.8</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 젠서은행(국유 대형은행): 7/28 A주 역대 신고가·600억 2차자본채 발행 후 고배당 수급 지속, 신고가 보합</t>
         </is>
@@ -13847,15 +14485,18 @@
         <v>15.7</v>
       </c>
       <c r="J5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>6.1</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -13896,19 +14537,18 @@
         <v>21.9</v>
       </c>
       <c r="J6" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="K6" t="n">
         <v>27</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -13947,15 +14587,18 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.9</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) (우량 주식은행·자오상은행): 기술주 대피 자금이 고배당 은행주로 이동, 배당 매력에 신고가</t>
         </is>
@@ -14000,15 +14643,18 @@
         <v>91</v>
       </c>
       <c r="J8" t="n">
+        <v>242.7</v>
+      </c>
+      <c r="K8" t="n">
         <v>50.9</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -14047,19 +14693,22 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.9</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) (가전 대표주·메이디그룹): 이구환신 수혜 기대·기술섹터 폭락 반사 순환매로 신고가</t>
         </is>
@@ -14101,20 +14750,17 @@
         <v>92.2</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>0.6</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -14155,19 +14801,18 @@
         <v>19.5</v>
       </c>
       <c r="J11" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="K11" t="n">
         <v>25.3</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14206,15 +14851,18 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.6</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14255,19 +14903,18 @@
         <v>5.5</v>
       </c>
       <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -14308,15 +14955,18 @@
         <v>28.9</v>
       </c>
       <c r="J14" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="K14" t="n">
         <v>13</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 둥산징미(PCB·광모듈): CPO·1.6T 광모듈 가격급락 루머+회사 단가하락 발언, CPO/PCB 연속 하한가권</t>
         </is>
@@ -14359,19 +15009,18 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.4</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -14409,16 +15058,17 @@
         <v>39.4</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
         <v>22</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) (국산 GPU·무어스레드): AI 하드웨어 섹터 전반 폭락 속 고평가 국산 GPU주 동반 급락</t>
         </is>
@@ -14463,15 +15113,18 @@
         <v>10.4</v>
       </c>
       <c r="J17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -14510,15 +15163,18 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K18" t="n">
         <v>1.6</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>(전일) 거리전기(에어컨 제조): AI·반도체주 급락 속 대소비재 역방향 강세, 이구환신(가전 교체보조) 확대 기대</t>
         </is>
@@ -14563,19 +15219,18 @@
         <v>5.7</v>
       </c>
       <c r="J19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -14616,15 +15271,18 @@
         <v>34.3</v>
       </c>
       <c r="J20" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="K20" t="n">
         <v>10.5</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -14665,15 +15323,18 @@
         <v>24.4</v>
       </c>
       <c r="J21" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="K21" t="n">
         <v>11.1</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -14712,15 +15373,18 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="K22" t="n">
         <v>7.8</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -14759,15 +15423,18 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K23" t="n">
         <v>1.7</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>(전일) (가전 대형주·하이얼스마트홈): 이구환신 정책 수혜·기술주 급락 반사 방어주 순환매로 신고가</t>
         </is>
@@ -14812,19 +15479,22 @@
         <v>15.2</v>
       </c>
       <c r="J24" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K24" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>(전일) 성훙커지A(PCB): 둥산징미 등 CPO 섹터 연속 급락 여파로 PCB 개념주 동반 하락, 섹터 수급 이탈</t>
         </is>
@@ -14869,17 +15539,20 @@
         <v>37.8</v>
       </c>
       <c r="J25" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="K25" t="n">
         <v>29.1</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
         </is>
       </c>
     </row>
@@ -14919,24 +15592,21 @@
         <v>26.6</v>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
         <v>4.1</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -14975,15 +15645,18 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>(전일) 중궈중처(철도차량 제조): 2Q 신규수주 516억위안(2025매출 18.9%) 모멘텀 지속, 대소비재 강세 속 신고가</t>
         </is>
@@ -15026,19 +15699,18 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="K28" t="n">
         <v>50</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -15079,15 +15751,18 @@
         <v>26.3</v>
       </c>
       <c r="J29" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="K29" t="n">
         <v>15.3</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>(전일) (광섬유 제조·창페이광섬유): 6월 고점 이후 광통신 섹터 조정 지속, 신규 촉매 없이 약세 연장</t>
         </is>
@@ -15130,19 +15805,18 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K30" t="n">
         <v>1.8</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -15181,15 +15855,18 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.6</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>(전일) (광섬유 광케이블·헝퉁광전): AI 연산 수요 불확실·한국 광통신주 동반 하락으로 급락</t>
         </is>
@@ -15232,15 +15909,18 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="K32" t="n">
         <v>10.3</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -15278,16 +15958,17 @@
         <v>15.9</v>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
         <v>8.1</v>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -15325,18 +16006,19 @@
         <v>15</v>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
         <v>28.4</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
         </is>
       </c>
     </row>
@@ -15377,15 +16059,18 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
+        <v>52</v>
+      </c>
+      <c r="K35" t="n">
         <v>17.5</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -15424,15 +16109,18 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K36" t="n">
         <v>2.5</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -15473,15 +16161,18 @@
         <v>33.5</v>
       </c>
       <c r="J37" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K37" t="n">
         <v>6.6</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -15521,16 +16212,17 @@
       <c r="I38" t="n">
         <v>23.3</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
         <v>3.9</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -15571,15 +16263,18 @@
         <v>16.7</v>
       </c>
       <c r="J39" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K39" t="n">
         <v>1.8</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -15618,15 +16313,18 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
+        <v>659.3</v>
+      </c>
+      <c r="K40" t="n">
         <v>7.8</v>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -15667,19 +16365,22 @@
         <v>22.7</v>
       </c>
       <c r="J41" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="K41" t="n">
         <v>3.1</v>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -15718,17 +16419,20 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
+        <v>41</v>
+      </c>
+      <c r="K42" t="n">
         <v>11.1</v>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
         </is>
       </c>
     </row>
@@ -15768,20 +16472,21 @@
         <v>11.4</v>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
         <v>13.2</v>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>(전일) (우주·특수전원): 상장 초 급등 후 조정 지속, 신규 재료 없음(IPO 거품 해소)</t>
         </is>
@@ -15826,15 +16531,18 @@
         <v>48.7</v>
       </c>
       <c r="J44" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="K44" t="n">
         <v>3.1</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -15873,15 +16581,18 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K45" t="n">
         <v>3.5</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>(전일) 중차이커지(유리섬유·AI전자포): 유상증자(44.8억위안) 희석 우려+AI하드웨어 조정 지속, 과창50 -4% 여파 신저가</t>
         </is>
@@ -15924,15 +16635,18 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -15972,20 +16686,17 @@
       <c r="I47" t="n">
         <v>235.5</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
         <v>36.9</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr">
-        <is>
-          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -16024,18 +16735,21 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K48" t="n">
         <v>13.5</v>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M48"/>
+  <autoFilter ref="A1:N48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/신고신저가_20260731.xlsx
+++ b/신고신저가_20260731.xlsx
@@ -7807,7 +7807,11 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>메타(소셜미디어·AI인프라): 2분기 EPS 컨센 하회·AI지출 급증으로 잉여현금 -91%, 3분기 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -8017,7 +8021,11 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>알트리아(말보로 담배·니코틴파우치): 2분기 EPS 소폭 하회·파우치 매출 -5%, 가이던스 실망</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8179,7 +8187,11 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -8445,7 +8457,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>L3해리스(방위 전자·통신): 연간 매출 가이던스 컨센 하회·미사일 사업부 IPO 연기 발표</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -8549,7 +8565,11 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="10" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>치폴레(패스트캐주얼 멕시칸): 2분기 소폭 상회·동일점포 +2.2% 회복, 연간 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8713,7 +8733,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="10" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -8769,7 +8793,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>알닐람(RNAi 치료제): 대표약 Amvuttra 매출 컨센서스 하회, ATTR 연간 가이던스 하향에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9199,7 +9227,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="10" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>아르시스(항공우주·방산 부품): 2분기 매출 $501M(+25%)·FCF 급증, FY26 가이던스 대폭 상회</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9413,7 +9445,11 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="10" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>CH로빈슨(화물 중개 물류): 배심원단 $604M 배상 판결·목표가 하향, 연속 하락 심화</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9575,7 +9611,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="10" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -9835,7 +9875,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="10" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>매디슨에어(냉난방 덕트·기류제어): 2분기 매출 +21%에도 EBITDA 가이던스 동결·마진 하락에 실망</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -10001,7 +10045,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="10" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>백스터(병원용 수액·의료기기): 2분기 EPS $0.56로 컨센서스 대폭 상회, FY26 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -10327,7 +10375,7 @@
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>(전일) 왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
+          <t>왓스코(냉난방 장비 유통): 2분기 EPS 컨센 하회·마진 축소(관세·가격효과 소멸)로 급락</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10433,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="10" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>코셉트테라퓨틱스(쿠싱증후군 치료제 코를림): 2분기 매출 $256M로 컨센서스 +17% 상회, 연간 가이던스 상향에 급등</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -11236,7 +11288,11 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>키오시아(낸드 메모리): AI 설비투자 피크아웃 우려·중국 공급과잉 경계로 신저가 경신, 당일 소폭 반등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -11500,7 +11556,11 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>NEC(IT서비스·방산): 1분기 순이익 2.6배·통기 매출 400억엔 상향 수정으로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -11776,7 +11836,11 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="10" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>JX어드밴스드메탈(구리·반도체소재): 반도체 관련주 조정 국면, 5월 고점 대비 40% 하락 52주 저가권</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -12154,7 +12218,11 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>주부전력(전력): 1분기 영업손실 전락·통기 경상이익 36% 하향·LNG 비용 급증에 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -12532,7 +12600,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="10" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>킷코만(간장·조미료): 북미 공장증설·해외 매출 견조로 중장기 신고가 흐름, 당일 소폭 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -12584,7 +12656,11 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="10" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>젠쇼HD(외식체인 스키야·하마즈시): 영업이익 13% 증가 전망·외식수요 회복에 신고가, 당일 소폭 조정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N29"/>
@@ -12799,7 +12875,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>농업은행(국유 상업은행): 5대 국유은행 H주 일제히 역사적 신고가, 고배당·안전자산 이동 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -12957,7 +13037,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>(전일) SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
+          <t>중신궈지(파운드리 반도체): 미 필라델피아 반도체지수 -5%·글로벌 AI 하드웨어 조정에 동조 하락</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13259,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>싼환그룹(전자 세라믹 부품 1위): 7월 상장 후 공모가 하회 흐름 지속, 당일 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -13341,7 +13425,11 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>민생은행(주식제 상업은행): 은행 섹터 전반 강세에 동반 상승, 개별 신규 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -13395,7 +13483,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
+          <t>창페이광섬유(광섬유·광케이블): 경쟁사 대규모 증설에 공급과잉 우려, 6월 고점 대비 반토막 지속</t>
         </is>
       </c>
     </row>
@@ -13735,7 +13823,11 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>톈수즈신(국산 AI연산 GPU): 매출 고성장에도 연간 적자 지속, 반도체 섹터 전반 급락에 동조</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -13791,7 +13883,7 @@
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>(전일) 한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
+          <t>한촨CNC(PCB 드릴링 장비): AI 투자기대 균열 우려에 PCB 장비주 전반 급락 동조</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14221,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>넥스칩(파운드리·디스플레이 구동칩): 7월 홍콩 신규 상장주, 반도체 섹터 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -14179,7 +14275,11 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="10" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N28"/>
@@ -14548,7 +14648,11 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>중지쉬촹(광모듈): 홍콩 상장 첫날 공모가 하회, A주도 연동 -15% 급락으로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14760,7 +14864,11 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>교통은행(국유 상업은행): 배당수익률 5%대·저평가 매력, 방어주 선호 자금유입으로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -14812,7 +14920,11 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>신이성(광모듈·광통신부품): 광모듈 3대 대장주 동반 급락 지속, AI 수요둔화·가격경쟁 우려</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14914,7 +15026,11 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>싱예은행(주식제 상업은행): 배당비율 30% 돌파·PBR 0.54배 저평가, 방어주 자금유입에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -15020,7 +15136,11 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>푸파은행(시중은행): 상장은행 배당 6456억위안 사상최대, 기술주 약세 속 고배당 순환매로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -15230,7 +15350,11 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -15552,7 +15676,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
+          <t>톈푸퉁신(광통신 패시브 부품): 7월28일 -13% 급락 후 연속 약세, 광모듈 섹터 조정 지속</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15730,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>후이커(LCD 패널·디스플레이): 상장 1개월 신규주, 상반기 순이익 최대 14% 감소 발표 후 연속 약세</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -15710,7 +15838,11 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="10" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>위안제반도체(광칩·레이저다이오드): PER 659배 과대평가 부담, 광모듈 섹터 밸류 조정에 연속 급락</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -15816,7 +15948,11 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="10" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>궈터우전력(수력발전): 야룽강 수력 독점 고배당 유틸리티, 기술주 약세 속 방어주 순환매</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -16018,7 +16154,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>(전일) 신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
+          <t>신위안구펀(IC설계 팹리스): 반도체 섹터 급락(과창판지수 -5%)·기술주 디레이팅에 연속 낙폭</t>
         </is>
       </c>
     </row>
@@ -16432,7 +16568,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
+          <t>성이전자(PCB 인쇄회로기판): PCB 섹터 기술주 조정 동반, 과창판지수 급락 속 연속 약세</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16832,11 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="10" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>뤄보터커(반도체 장비·실리콘포토닉스): 1분기 순이익 적자 지속, 광모듈 장비 섹터 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
